--- a/templates/salary_map_template.xlsx
+++ b/templates/salary_map_template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\F. Martins\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{462811E6-2D08-4E70-B0F1-6C29AF3CD75F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D88600A-CA34-421E-82A0-D5D251FEB78A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Folha1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>Subsídio de Turno</t>
   </si>
@@ -81,12 +81,18 @@
       <t>"Cruz Lusa"</t>
     </r>
   </si>
+  <si>
+    <t>Mês Atual</t>
+  </si>
+  <si>
+    <t>Mês Anterior</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -152,6 +158,19 @@
     <font>
       <sz val="18"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -342,7 +361,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -358,44 +377,99 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="11">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="5"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -415,6 +489,13 @@
         <b/>
         <i val="0"/>
         <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
       </font>
     </dxf>
   </dxfs>
@@ -484,13 +565,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>8</xdr:col>
+      <xdr:col>9</xdr:col>
       <xdr:colOff>419100</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>19050</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
+      <xdr:col>10</xdr:col>
       <xdr:colOff>18419</xdr:colOff>
       <xdr:row>5</xdr:row>
       <xdr:rowOff>25400</xdr:rowOff>
@@ -795,489 +876,541 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:J221"/>
+  <dimension ref="A2:K222"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="17.25" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2.85546875" customWidth="1"/>
     <col min="2" max="2" width="24.140625" customWidth="1"/>
-    <col min="3" max="4" width="21.42578125" style="1" customWidth="1"/>
-    <col min="5" max="9" width="21.42578125" customWidth="1"/>
-    <col min="10" max="10" width="2.85546875" customWidth="1"/>
-    <col min="11" max="16384" width="9.140625" hidden="1"/>
+    <col min="3" max="4" width="14.28515625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="21.42578125" style="1" customWidth="1"/>
+    <col min="6" max="10" width="21.42578125" customWidth="1"/>
+    <col min="11" max="11" width="2.85546875" customWidth="1"/>
+    <col min="12" max="16384" width="9.140625" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:10" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C2" s="4" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="3" spans="2:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D2" s="4"/>
+    </row>
+    <row r="3" spans="2:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C3" s="5" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="4" spans="2:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D3" s="5"/>
+    </row>
+    <row r="4" spans="2:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C4" s="6" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="6" spans="2:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="16"/>
-      <c r="C6" s="16"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="16"/>
-      <c r="F6" s="16"/>
-      <c r="G6" s="16"/>
-      <c r="H6" s="16"/>
-      <c r="I6" s="16"/>
-    </row>
-    <row r="7" spans="2:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="17"/>
-      <c r="C7" s="17"/>
-      <c r="D7" s="17"/>
-      <c r="E7" s="17"/>
-      <c r="F7" s="17"/>
-      <c r="G7" s="17"/>
-      <c r="H7" s="17"/>
-      <c r="I7" s="17"/>
-    </row>
-    <row r="8" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="3" t="s">
+      <c r="D4" s="6"/>
+    </row>
+    <row r="6" spans="2:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="7"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7"/>
+      <c r="I6" s="7"/>
+      <c r="J6" s="7"/>
+    </row>
+    <row r="7" spans="2:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
+    </row>
+    <row r="8" spans="2:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D8" s="9"/>
+      <c r="E8" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="F8" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="F8" s="3" t="s">
+      <c r="G8" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="H8" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="H8" s="3" t="s">
+      <c r="I8" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="I8" s="3" t="s">
+      <c r="J8" s="9" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B9" s="7"/>
-      <c r="C9" s="10"/>
-      <c r="D9" s="10"/>
-      <c r="E9" s="10"/>
-      <c r="F9" s="10"/>
-      <c r="G9" s="10"/>
-      <c r="H9" s="10"/>
-      <c r="I9" s="11"/>
-    </row>
-    <row r="10" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B10" s="8"/>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="12"/>
-      <c r="H10" s="12"/>
-      <c r="I10" s="13"/>
-    </row>
-    <row r="11" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B11" s="8"/>
-      <c r="C11" s="12"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="12"/>
-      <c r="H11" s="12"/>
-      <c r="I11" s="13"/>
-    </row>
-    <row r="12" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B12" s="8"/>
-      <c r="C12" s="12"/>
-      <c r="D12" s="12"/>
-      <c r="E12" s="12"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="12"/>
-      <c r="H12" s="12"/>
-      <c r="I12" s="13"/>
-    </row>
-    <row r="13" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B13" s="8"/>
-      <c r="C13" s="12"/>
-      <c r="D13" s="12"/>
-      <c r="E13" s="12"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="12"/>
-      <c r="H13" s="12"/>
-      <c r="I13" s="13"/>
-    </row>
-    <row r="14" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B14" s="8"/>
-      <c r="C14" s="12"/>
-      <c r="D14" s="12"/>
-      <c r="E14" s="12"/>
-      <c r="F14" s="12"/>
-      <c r="G14" s="12"/>
-      <c r="H14" s="12"/>
-      <c r="I14" s="13"/>
-    </row>
-    <row r="15" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B15" s="8"/>
-      <c r="C15" s="12"/>
-      <c r="D15" s="12"/>
-      <c r="E15" s="12"/>
-      <c r="F15" s="12"/>
-      <c r="G15" s="12"/>
-      <c r="H15" s="12"/>
-      <c r="I15" s="13"/>
-    </row>
-    <row r="16" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B16" s="8"/>
-      <c r="C16" s="12"/>
-      <c r="D16" s="12"/>
-      <c r="E16" s="12"/>
-      <c r="F16" s="12"/>
-      <c r="G16" s="12"/>
-      <c r="H16" s="12"/>
-      <c r="I16" s="13"/>
-    </row>
-    <row r="17" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B17" s="8"/>
-      <c r="C17" s="12"/>
-      <c r="D17" s="12"/>
-      <c r="E17" s="12"/>
-      <c r="F17" s="12"/>
-      <c r="G17" s="12"/>
-      <c r="H17" s="12"/>
-      <c r="I17" s="13"/>
-    </row>
-    <row r="18" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B18" s="8"/>
-      <c r="C18" s="12"/>
-      <c r="D18" s="12"/>
-      <c r="E18" s="12"/>
-      <c r="F18" s="12"/>
-      <c r="G18" s="12"/>
-      <c r="H18" s="12"/>
-      <c r="I18" s="13"/>
-    </row>
-    <row r="19" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B19" s="8"/>
-      <c r="C19" s="12"/>
-      <c r="D19" s="12"/>
-      <c r="E19" s="12"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="12"/>
-      <c r="H19" s="12"/>
-      <c r="I19" s="13"/>
-    </row>
-    <row r="20" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B20" s="8"/>
-      <c r="C20" s="12"/>
-      <c r="D20" s="12"/>
-      <c r="E20" s="12"/>
-      <c r="F20" s="12"/>
-      <c r="G20" s="12"/>
-      <c r="H20" s="12"/>
-      <c r="I20" s="13"/>
-    </row>
-    <row r="21" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B21" s="8"/>
-      <c r="C21" s="12"/>
-      <c r="D21" s="12"/>
-      <c r="E21" s="12"/>
-      <c r="F21" s="12"/>
-      <c r="G21" s="12"/>
-      <c r="H21" s="12"/>
-      <c r="I21" s="13"/>
-    </row>
-    <row r="22" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B22" s="8"/>
-      <c r="C22" s="12"/>
-      <c r="D22" s="12"/>
-      <c r="E22" s="12"/>
-      <c r="F22" s="12"/>
-      <c r="G22" s="12"/>
-      <c r="H22" s="12"/>
-      <c r="I22" s="13"/>
-    </row>
-    <row r="23" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B23" s="8"/>
-      <c r="C23" s="12"/>
-      <c r="D23" s="12"/>
-      <c r="E23" s="12"/>
-      <c r="F23" s="12"/>
-      <c r="G23" s="12"/>
-      <c r="H23" s="12"/>
-      <c r="I23" s="13"/>
-    </row>
-    <row r="24" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B24" s="8"/>
-      <c r="C24" s="12"/>
-      <c r="D24" s="12"/>
-      <c r="E24" s="12"/>
-      <c r="F24" s="12"/>
-      <c r="G24" s="12"/>
-      <c r="H24" s="12"/>
-      <c r="I24" s="13"/>
-    </row>
-    <row r="25" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B25" s="8"/>
-      <c r="C25" s="12"/>
-      <c r="D25" s="12"/>
-      <c r="E25" s="12"/>
-      <c r="F25" s="12"/>
-      <c r="G25" s="12"/>
-      <c r="H25" s="12"/>
-      <c r="I25" s="13"/>
-    </row>
-    <row r="26" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B26" s="8"/>
-      <c r="C26" s="12"/>
-      <c r="D26" s="12"/>
-      <c r="E26" s="12"/>
-      <c r="F26" s="12"/>
-      <c r="G26" s="12"/>
-      <c r="H26" s="12"/>
-      <c r="I26" s="13"/>
-    </row>
-    <row r="27" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B27" s="8"/>
-      <c r="C27" s="12"/>
-      <c r="D27" s="12"/>
-      <c r="E27" s="12"/>
-      <c r="F27" s="12"/>
-      <c r="G27" s="12"/>
-      <c r="H27" s="12"/>
-      <c r="I27" s="13"/>
-    </row>
-    <row r="28" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B28" s="8"/>
-      <c r="C28" s="12"/>
-      <c r="D28" s="12"/>
-      <c r="E28" s="12"/>
-      <c r="F28" s="12"/>
-      <c r="G28" s="12"/>
-      <c r="H28" s="12"/>
-      <c r="I28" s="13"/>
-    </row>
-    <row r="29" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B29" s="8"/>
-      <c r="C29" s="12"/>
-      <c r="D29" s="12"/>
-      <c r="E29" s="12"/>
-      <c r="F29" s="12"/>
-      <c r="G29" s="12"/>
-      <c r="H29" s="12"/>
-      <c r="I29" s="13"/>
-    </row>
-    <row r="30" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B30" s="8"/>
-      <c r="C30" s="12"/>
-      <c r="D30" s="12"/>
-      <c r="E30" s="12"/>
-      <c r="F30" s="12"/>
-      <c r="G30" s="12"/>
-      <c r="H30" s="12"/>
-      <c r="I30" s="13"/>
-    </row>
-    <row r="31" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B31" s="8"/>
-      <c r="C31" s="12"/>
-      <c r="D31" s="12"/>
-      <c r="E31" s="12"/>
-      <c r="F31" s="12"/>
-      <c r="G31" s="12"/>
-      <c r="H31" s="12"/>
-      <c r="I31" s="13"/>
-    </row>
-    <row r="32" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B32" s="8"/>
-      <c r="C32" s="12"/>
-      <c r="D32" s="12"/>
-      <c r="E32" s="12"/>
-      <c r="F32" s="12"/>
-      <c r="G32" s="12"/>
-      <c r="H32" s="12"/>
-      <c r="I32" s="13"/>
-    </row>
-    <row r="33" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B33" s="8"/>
-      <c r="C33" s="12"/>
-      <c r="D33" s="12"/>
-      <c r="E33" s="12"/>
-      <c r="F33" s="12"/>
-      <c r="G33" s="12"/>
-      <c r="H33" s="12"/>
-      <c r="I33" s="13"/>
-    </row>
-    <row r="34" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B34" s="8"/>
-      <c r="C34" s="12"/>
-      <c r="D34" s="12"/>
-      <c r="E34" s="12"/>
-      <c r="F34" s="12"/>
-      <c r="G34" s="12"/>
-      <c r="H34" s="12"/>
-      <c r="I34" s="13"/>
-    </row>
-    <row r="35" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B35" s="8"/>
-      <c r="C35" s="12"/>
-      <c r="D35" s="12"/>
-      <c r="E35" s="12"/>
-      <c r="F35" s="12"/>
-      <c r="G35" s="12"/>
-      <c r="H35" s="12"/>
-      <c r="I35" s="13"/>
-    </row>
-    <row r="36" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B36" s="8"/>
-      <c r="C36" s="12"/>
-      <c r="D36" s="12"/>
-      <c r="E36" s="12"/>
-      <c r="F36" s="12"/>
-      <c r="G36" s="12"/>
-      <c r="H36" s="12"/>
-      <c r="I36" s="13"/>
-    </row>
-    <row r="37" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B37" s="8"/>
-      <c r="C37" s="12"/>
-      <c r="D37" s="12"/>
-      <c r="E37" s="12"/>
-      <c r="F37" s="12"/>
-      <c r="G37" s="12"/>
-      <c r="H37" s="12"/>
-      <c r="I37" s="13"/>
-    </row>
-    <row r="38" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B38" s="8"/>
-      <c r="C38" s="12"/>
-      <c r="D38" s="12"/>
-      <c r="E38" s="12"/>
-      <c r="F38" s="12"/>
-      <c r="G38" s="12"/>
-      <c r="H38" s="12"/>
-      <c r="I38" s="13"/>
-    </row>
-    <row r="39" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B39" s="8"/>
-      <c r="C39" s="12"/>
-      <c r="D39" s="12"/>
-      <c r="E39" s="12"/>
-      <c r="F39" s="12"/>
-      <c r="G39" s="12"/>
-      <c r="H39" s="12"/>
-      <c r="I39" s="13"/>
-    </row>
-    <row r="40" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B40" s="8"/>
-      <c r="C40" s="12"/>
-      <c r="D40" s="12"/>
-      <c r="E40" s="12"/>
-      <c r="F40" s="12"/>
-      <c r="G40" s="12"/>
-      <c r="H40" s="12"/>
-      <c r="I40" s="13"/>
-    </row>
-    <row r="41" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B41" s="8"/>
-      <c r="C41" s="12"/>
-      <c r="D41" s="12"/>
-      <c r="E41" s="12"/>
-      <c r="F41" s="12"/>
-      <c r="G41" s="12"/>
-      <c r="H41" s="12"/>
-      <c r="I41" s="13"/>
-    </row>
-    <row r="42" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B42" s="8"/>
-      <c r="C42" s="12"/>
-      <c r="D42" s="12"/>
-      <c r="E42" s="12"/>
-      <c r="F42" s="12"/>
-      <c r="G42" s="12"/>
-      <c r="H42" s="12"/>
-      <c r="I42" s="13"/>
-    </row>
-    <row r="43" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B43" s="8"/>
-      <c r="C43" s="12"/>
-      <c r="D43" s="12"/>
-      <c r="E43" s="12"/>
-      <c r="F43" s="12"/>
-      <c r="G43" s="12"/>
-      <c r="H43" s="12"/>
-      <c r="I43" s="13"/>
-    </row>
-    <row r="44" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B44" s="8"/>
-      <c r="C44" s="12"/>
-      <c r="D44" s="12"/>
-      <c r="E44" s="12"/>
-      <c r="F44" s="12"/>
-      <c r="G44" s="12"/>
-      <c r="H44" s="12"/>
-      <c r="I44" s="13"/>
-    </row>
-    <row r="45" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B45" s="8"/>
-      <c r="C45" s="12"/>
-      <c r="D45" s="12"/>
-      <c r="E45" s="12"/>
-      <c r="F45" s="12"/>
-      <c r="G45" s="12"/>
-      <c r="H45" s="12"/>
-      <c r="I45" s="13"/>
-    </row>
-    <row r="46" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B46" s="8"/>
-      <c r="C46" s="12"/>
-      <c r="D46" s="12"/>
-      <c r="E46" s="12"/>
-      <c r="F46" s="12"/>
-      <c r="G46" s="12"/>
-      <c r="H46" s="12"/>
-      <c r="I46" s="13"/>
-    </row>
-    <row r="47" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B47" s="8"/>
-      <c r="C47" s="12"/>
-      <c r="D47" s="12"/>
-      <c r="E47" s="12"/>
-      <c r="F47" s="12"/>
-      <c r="G47" s="12"/>
-      <c r="H47" s="12"/>
-      <c r="I47" s="13"/>
-    </row>
-    <row r="48" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B48" s="9"/>
-      <c r="C48" s="14"/>
-      <c r="D48" s="14"/>
-      <c r="E48" s="14"/>
-      <c r="F48" s="14"/>
-      <c r="G48" s="14"/>
-      <c r="H48" s="14"/>
-      <c r="I48" s="15"/>
-    </row>
-    <row r="49" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B49" s="2"/>
-      <c r="C49" s="2"/>
-      <c r="D49" s="2"/>
-      <c r="E49" s="2"/>
-      <c r="F49" s="2"/>
-      <c r="G49" s="2"/>
-      <c r="H49" s="2"/>
-      <c r="I49" s="2"/>
-    </row>
-    <row r="50" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="9"/>
+      <c r="C9" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9" s="9"/>
+      <c r="F9" s="9"/>
+      <c r="G9" s="9"/>
+      <c r="H9" s="9"/>
+      <c r="I9" s="9"/>
+      <c r="J9" s="9"/>
+    </row>
+    <row r="10" spans="2:10" ht="15" x14ac:dyDescent="0.25">
+      <c r="B10" s="13"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="10"/>
+      <c r="F10" s="10"/>
+      <c r="G10" s="10"/>
+      <c r="H10" s="10"/>
+      <c r="I10" s="10"/>
+      <c r="J10" s="14"/>
+    </row>
+    <row r="11" spans="2:10" ht="15" x14ac:dyDescent="0.25">
+      <c r="B11" s="15"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="11"/>
+      <c r="I11" s="11"/>
+      <c r="J11" s="16"/>
+    </row>
+    <row r="12" spans="2:10" ht="15" x14ac:dyDescent="0.25">
+      <c r="B12" s="15"/>
+      <c r="C12" s="11"/>
+      <c r="D12" s="11"/>
+      <c r="E12" s="11"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="11"/>
+      <c r="H12" s="11"/>
+      <c r="I12" s="11"/>
+      <c r="J12" s="16"/>
+    </row>
+    <row r="13" spans="2:10" ht="15" x14ac:dyDescent="0.25">
+      <c r="B13" s="15"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="11"/>
+      <c r="H13" s="11"/>
+      <c r="I13" s="11"/>
+      <c r="J13" s="16"/>
+    </row>
+    <row r="14" spans="2:10" ht="15" x14ac:dyDescent="0.25">
+      <c r="B14" s="15"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="11"/>
+      <c r="H14" s="11"/>
+      <c r="I14" s="11"/>
+      <c r="J14" s="16"/>
+    </row>
+    <row r="15" spans="2:10" ht="15" x14ac:dyDescent="0.25">
+      <c r="B15" s="15"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="11"/>
+      <c r="I15" s="11"/>
+      <c r="J15" s="16"/>
+    </row>
+    <row r="16" spans="2:10" ht="15" x14ac:dyDescent="0.25">
+      <c r="B16" s="15"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="11"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="11"/>
+      <c r="H16" s="11"/>
+      <c r="I16" s="11"/>
+      <c r="J16" s="16"/>
+    </row>
+    <row r="17" spans="2:10" ht="15" x14ac:dyDescent="0.25">
+      <c r="B17" s="15"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="11"/>
+      <c r="F17" s="11"/>
+      <c r="G17" s="11"/>
+      <c r="H17" s="11"/>
+      <c r="I17" s="11"/>
+      <c r="J17" s="16"/>
+    </row>
+    <row r="18" spans="2:10" ht="15" x14ac:dyDescent="0.25">
+      <c r="B18" s="15"/>
+      <c r="C18" s="11"/>
+      <c r="D18" s="11"/>
+      <c r="E18" s="11"/>
+      <c r="F18" s="11"/>
+      <c r="G18" s="11"/>
+      <c r="H18" s="11"/>
+      <c r="I18" s="11"/>
+      <c r="J18" s="16"/>
+    </row>
+    <row r="19" spans="2:10" ht="15" x14ac:dyDescent="0.25">
+      <c r="B19" s="15"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="11"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="11"/>
+      <c r="H19" s="11"/>
+      <c r="I19" s="11"/>
+      <c r="J19" s="16"/>
+    </row>
+    <row r="20" spans="2:10" ht="15" x14ac:dyDescent="0.25">
+      <c r="B20" s="15"/>
+      <c r="C20" s="11"/>
+      <c r="D20" s="11"/>
+      <c r="E20" s="11"/>
+      <c r="F20" s="11"/>
+      <c r="G20" s="11"/>
+      <c r="H20" s="11"/>
+      <c r="I20" s="11"/>
+      <c r="J20" s="16"/>
+    </row>
+    <row r="21" spans="2:10" ht="15" x14ac:dyDescent="0.25">
+      <c r="B21" s="15"/>
+      <c r="C21" s="11"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="11"/>
+      <c r="F21" s="11"/>
+      <c r="G21" s="11"/>
+      <c r="H21" s="11"/>
+      <c r="I21" s="11"/>
+      <c r="J21" s="16"/>
+    </row>
+    <row r="22" spans="2:10" ht="15" x14ac:dyDescent="0.25">
+      <c r="B22" s="15"/>
+      <c r="C22" s="11"/>
+      <c r="D22" s="11"/>
+      <c r="E22" s="11"/>
+      <c r="F22" s="11"/>
+      <c r="G22" s="11"/>
+      <c r="H22" s="11"/>
+      <c r="I22" s="11"/>
+      <c r="J22" s="16"/>
+    </row>
+    <row r="23" spans="2:10" ht="15" x14ac:dyDescent="0.25">
+      <c r="B23" s="15"/>
+      <c r="C23" s="11"/>
+      <c r="D23" s="11"/>
+      <c r="E23" s="11"/>
+      <c r="F23" s="11"/>
+      <c r="G23" s="11"/>
+      <c r="H23" s="11"/>
+      <c r="I23" s="11"/>
+      <c r="J23" s="16"/>
+    </row>
+    <row r="24" spans="2:10" ht="15" x14ac:dyDescent="0.25">
+      <c r="B24" s="15"/>
+      <c r="C24" s="11"/>
+      <c r="D24" s="11"/>
+      <c r="E24" s="11"/>
+      <c r="F24" s="11"/>
+      <c r="G24" s="11"/>
+      <c r="H24" s="11"/>
+      <c r="I24" s="11"/>
+      <c r="J24" s="16"/>
+    </row>
+    <row r="25" spans="2:10" ht="15" x14ac:dyDescent="0.25">
+      <c r="B25" s="15"/>
+      <c r="C25" s="11"/>
+      <c r="D25" s="11"/>
+      <c r="E25" s="11"/>
+      <c r="F25" s="11"/>
+      <c r="G25" s="11"/>
+      <c r="H25" s="11"/>
+      <c r="I25" s="11"/>
+      <c r="J25" s="16"/>
+    </row>
+    <row r="26" spans="2:10" ht="15" x14ac:dyDescent="0.25">
+      <c r="B26" s="15"/>
+      <c r="C26" s="11"/>
+      <c r="D26" s="11"/>
+      <c r="E26" s="11"/>
+      <c r="F26" s="11"/>
+      <c r="G26" s="11"/>
+      <c r="H26" s="11"/>
+      <c r="I26" s="11"/>
+      <c r="J26" s="16"/>
+    </row>
+    <row r="27" spans="2:10" ht="15" x14ac:dyDescent="0.25">
+      <c r="B27" s="15"/>
+      <c r="C27" s="11"/>
+      <c r="D27" s="11"/>
+      <c r="E27" s="11"/>
+      <c r="F27" s="11"/>
+      <c r="G27" s="11"/>
+      <c r="H27" s="11"/>
+      <c r="I27" s="11"/>
+      <c r="J27" s="16"/>
+    </row>
+    <row r="28" spans="2:10" ht="15" x14ac:dyDescent="0.25">
+      <c r="B28" s="15"/>
+      <c r="C28" s="11"/>
+      <c r="D28" s="11"/>
+      <c r="E28" s="11"/>
+      <c r="F28" s="11"/>
+      <c r="G28" s="11"/>
+      <c r="H28" s="11"/>
+      <c r="I28" s="11"/>
+      <c r="J28" s="16"/>
+    </row>
+    <row r="29" spans="2:10" ht="15" x14ac:dyDescent="0.25">
+      <c r="B29" s="15"/>
+      <c r="C29" s="11"/>
+      <c r="D29" s="11"/>
+      <c r="E29" s="11"/>
+      <c r="F29" s="11"/>
+      <c r="G29" s="11"/>
+      <c r="H29" s="11"/>
+      <c r="I29" s="11"/>
+      <c r="J29" s="16"/>
+    </row>
+    <row r="30" spans="2:10" ht="15" x14ac:dyDescent="0.25">
+      <c r="B30" s="15"/>
+      <c r="C30" s="11"/>
+      <c r="D30" s="11"/>
+      <c r="E30" s="11"/>
+      <c r="F30" s="11"/>
+      <c r="G30" s="11"/>
+      <c r="H30" s="11"/>
+      <c r="I30" s="11"/>
+      <c r="J30" s="16"/>
+    </row>
+    <row r="31" spans="2:10" ht="15" x14ac:dyDescent="0.25">
+      <c r="B31" s="15"/>
+      <c r="C31" s="11"/>
+      <c r="D31" s="11"/>
+      <c r="E31" s="11"/>
+      <c r="F31" s="11"/>
+      <c r="G31" s="11"/>
+      <c r="H31" s="11"/>
+      <c r="I31" s="11"/>
+      <c r="J31" s="16"/>
+    </row>
+    <row r="32" spans="2:10" ht="15" x14ac:dyDescent="0.25">
+      <c r="B32" s="15"/>
+      <c r="C32" s="11"/>
+      <c r="D32" s="11"/>
+      <c r="E32" s="11"/>
+      <c r="F32" s="11"/>
+      <c r="G32" s="11"/>
+      <c r="H32" s="11"/>
+      <c r="I32" s="11"/>
+      <c r="J32" s="16"/>
+    </row>
+    <row r="33" spans="2:10" ht="15" x14ac:dyDescent="0.25">
+      <c r="B33" s="15"/>
+      <c r="C33" s="11"/>
+      <c r="D33" s="11"/>
+      <c r="E33" s="11"/>
+      <c r="F33" s="11"/>
+      <c r="G33" s="11"/>
+      <c r="H33" s="11"/>
+      <c r="I33" s="11"/>
+      <c r="J33" s="16"/>
+    </row>
+    <row r="34" spans="2:10" ht="15" x14ac:dyDescent="0.25">
+      <c r="B34" s="15"/>
+      <c r="C34" s="11"/>
+      <c r="D34" s="11"/>
+      <c r="E34" s="11"/>
+      <c r="F34" s="11"/>
+      <c r="G34" s="11"/>
+      <c r="H34" s="11"/>
+      <c r="I34" s="11"/>
+      <c r="J34" s="16"/>
+    </row>
+    <row r="35" spans="2:10" ht="15" x14ac:dyDescent="0.25">
+      <c r="B35" s="15"/>
+      <c r="C35" s="11"/>
+      <c r="D35" s="11"/>
+      <c r="E35" s="11"/>
+      <c r="F35" s="11"/>
+      <c r="G35" s="11"/>
+      <c r="H35" s="11"/>
+      <c r="I35" s="11"/>
+      <c r="J35" s="16"/>
+    </row>
+    <row r="36" spans="2:10" ht="15" x14ac:dyDescent="0.25">
+      <c r="B36" s="15"/>
+      <c r="C36" s="11"/>
+      <c r="D36" s="11"/>
+      <c r="E36" s="11"/>
+      <c r="F36" s="11"/>
+      <c r="G36" s="11"/>
+      <c r="H36" s="11"/>
+      <c r="I36" s="11"/>
+      <c r="J36" s="16"/>
+    </row>
+    <row r="37" spans="2:10" ht="15" x14ac:dyDescent="0.25">
+      <c r="B37" s="15"/>
+      <c r="C37" s="11"/>
+      <c r="D37" s="11"/>
+      <c r="E37" s="11"/>
+      <c r="F37" s="11"/>
+      <c r="G37" s="11"/>
+      <c r="H37" s="11"/>
+      <c r="I37" s="11"/>
+      <c r="J37" s="16"/>
+    </row>
+    <row r="38" spans="2:10" ht="15" x14ac:dyDescent="0.25">
+      <c r="B38" s="15"/>
+      <c r="C38" s="11"/>
+      <c r="D38" s="11"/>
+      <c r="E38" s="11"/>
+      <c r="F38" s="11"/>
+      <c r="G38" s="11"/>
+      <c r="H38" s="11"/>
+      <c r="I38" s="11"/>
+      <c r="J38" s="16"/>
+    </row>
+    <row r="39" spans="2:10" ht="15" x14ac:dyDescent="0.25">
+      <c r="B39" s="15"/>
+      <c r="C39" s="11"/>
+      <c r="D39" s="11"/>
+      <c r="E39" s="11"/>
+      <c r="F39" s="11"/>
+      <c r="G39" s="11"/>
+      <c r="H39" s="11"/>
+      <c r="I39" s="11"/>
+      <c r="J39" s="16"/>
+    </row>
+    <row r="40" spans="2:10" ht="15" x14ac:dyDescent="0.25">
+      <c r="B40" s="15"/>
+      <c r="C40" s="11"/>
+      <c r="D40" s="11"/>
+      <c r="E40" s="11"/>
+      <c r="F40" s="11"/>
+      <c r="G40" s="11"/>
+      <c r="H40" s="11"/>
+      <c r="I40" s="11"/>
+      <c r="J40" s="16"/>
+    </row>
+    <row r="41" spans="2:10" ht="15" x14ac:dyDescent="0.25">
+      <c r="B41" s="15"/>
+      <c r="C41" s="11"/>
+      <c r="D41" s="11"/>
+      <c r="E41" s="11"/>
+      <c r="F41" s="11"/>
+      <c r="G41" s="11"/>
+      <c r="H41" s="11"/>
+      <c r="I41" s="11"/>
+      <c r="J41" s="16"/>
+    </row>
+    <row r="42" spans="2:10" ht="15" x14ac:dyDescent="0.25">
+      <c r="B42" s="15"/>
+      <c r="C42" s="11"/>
+      <c r="D42" s="11"/>
+      <c r="E42" s="11"/>
+      <c r="F42" s="11"/>
+      <c r="G42" s="11"/>
+      <c r="H42" s="11"/>
+      <c r="I42" s="11"/>
+      <c r="J42" s="16"/>
+    </row>
+    <row r="43" spans="2:10" ht="15" x14ac:dyDescent="0.25">
+      <c r="B43" s="15"/>
+      <c r="C43" s="11"/>
+      <c r="D43" s="11"/>
+      <c r="E43" s="11"/>
+      <c r="F43" s="11"/>
+      <c r="G43" s="11"/>
+      <c r="H43" s="11"/>
+      <c r="I43" s="11"/>
+      <c r="J43" s="16"/>
+    </row>
+    <row r="44" spans="2:10" ht="15" x14ac:dyDescent="0.25">
+      <c r="B44" s="15"/>
+      <c r="C44" s="11"/>
+      <c r="D44" s="11"/>
+      <c r="E44" s="11"/>
+      <c r="F44" s="11"/>
+      <c r="G44" s="11"/>
+      <c r="H44" s="11"/>
+      <c r="I44" s="11"/>
+      <c r="J44" s="16"/>
+    </row>
+    <row r="45" spans="2:10" ht="15" x14ac:dyDescent="0.25">
+      <c r="B45" s="15"/>
+      <c r="C45" s="11"/>
+      <c r="D45" s="11"/>
+      <c r="E45" s="11"/>
+      <c r="F45" s="11"/>
+      <c r="G45" s="11"/>
+      <c r="H45" s="11"/>
+      <c r="I45" s="11"/>
+      <c r="J45" s="16"/>
+    </row>
+    <row r="46" spans="2:10" ht="15" x14ac:dyDescent="0.25">
+      <c r="B46" s="15"/>
+      <c r="C46" s="11"/>
+      <c r="D46" s="11"/>
+      <c r="E46" s="11"/>
+      <c r="F46" s="11"/>
+      <c r="G46" s="11"/>
+      <c r="H46" s="11"/>
+      <c r="I46" s="11"/>
+      <c r="J46" s="16"/>
+    </row>
+    <row r="47" spans="2:10" ht="15" x14ac:dyDescent="0.25">
+      <c r="B47" s="15"/>
+      <c r="C47" s="11"/>
+      <c r="D47" s="11"/>
+      <c r="E47" s="11"/>
+      <c r="F47" s="11"/>
+      <c r="G47" s="11"/>
+      <c r="H47" s="11"/>
+      <c r="I47" s="11"/>
+      <c r="J47" s="16"/>
+    </row>
+    <row r="48" spans="2:10" ht="15" x14ac:dyDescent="0.25">
+      <c r="B48" s="15"/>
+      <c r="C48" s="11"/>
+      <c r="D48" s="11"/>
+      <c r="E48" s="11"/>
+      <c r="F48" s="11"/>
+      <c r="G48" s="11"/>
+      <c r="H48" s="11"/>
+      <c r="I48" s="11"/>
+      <c r="J48" s="16"/>
+    </row>
+    <row r="49" spans="2:10" ht="15" x14ac:dyDescent="0.25">
+      <c r="B49" s="17"/>
+      <c r="C49" s="12"/>
+      <c r="D49" s="12"/>
+      <c r="E49" s="12"/>
+      <c r="F49" s="12"/>
+      <c r="G49" s="12"/>
+      <c r="H49" s="12"/>
+      <c r="I49" s="12"/>
+      <c r="J49" s="18"/>
+    </row>
+    <row r="50" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
       <c r="D50" s="2"/>
@@ -1286,8 +1419,9 @@
       <c r="G50" s="2"/>
       <c r="H50" s="2"/>
       <c r="I50" s="2"/>
-    </row>
-    <row r="51" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J50" s="2"/>
+    </row>
+    <row r="51" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B51" s="2"/>
       <c r="C51" s="2"/>
       <c r="D51" s="2"/>
@@ -1296,8 +1430,9 @@
       <c r="G51" s="2"/>
       <c r="H51" s="2"/>
       <c r="I51" s="2"/>
-    </row>
-    <row r="52" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J51" s="2"/>
+    </row>
+    <row r="52" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B52" s="2"/>
       <c r="C52" s="2"/>
       <c r="D52" s="2"/>
@@ -1306,8 +1441,9 @@
       <c r="G52" s="2"/>
       <c r="H52" s="2"/>
       <c r="I52" s="2"/>
-    </row>
-    <row r="53" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J52" s="2"/>
+    </row>
+    <row r="53" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B53" s="2"/>
       <c r="C53" s="2"/>
       <c r="D53" s="2"/>
@@ -1316,8 +1452,9 @@
       <c r="G53" s="2"/>
       <c r="H53" s="2"/>
       <c r="I53" s="2"/>
-    </row>
-    <row r="54" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J53" s="2"/>
+    </row>
+    <row r="54" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B54" s="2"/>
       <c r="C54" s="2"/>
       <c r="D54" s="2"/>
@@ -1326,8 +1463,9 @@
       <c r="G54" s="2"/>
       <c r="H54" s="2"/>
       <c r="I54" s="2"/>
-    </row>
-    <row r="55" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J54" s="2"/>
+    </row>
+    <row r="55" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B55" s="2"/>
       <c r="C55" s="2"/>
       <c r="D55" s="2"/>
@@ -1336,8 +1474,9 @@
       <c r="G55" s="2"/>
       <c r="H55" s="2"/>
       <c r="I55" s="2"/>
-    </row>
-    <row r="56" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J55" s="2"/>
+    </row>
+    <row r="56" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
       <c r="D56" s="2"/>
@@ -1346,8 +1485,9 @@
       <c r="G56" s="2"/>
       <c r="H56" s="2"/>
       <c r="I56" s="2"/>
-    </row>
-    <row r="57" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J56" s="2"/>
+    </row>
+    <row r="57" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B57" s="2"/>
       <c r="C57" s="2"/>
       <c r="D57" s="2"/>
@@ -1356,8 +1496,9 @@
       <c r="G57" s="2"/>
       <c r="H57" s="2"/>
       <c r="I57" s="2"/>
-    </row>
-    <row r="58" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J57" s="2"/>
+    </row>
+    <row r="58" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B58" s="2"/>
       <c r="C58" s="2"/>
       <c r="D58" s="2"/>
@@ -1366,8 +1507,9 @@
       <c r="G58" s="2"/>
       <c r="H58" s="2"/>
       <c r="I58" s="2"/>
-    </row>
-    <row r="59" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J58" s="2"/>
+    </row>
+    <row r="59" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B59" s="2"/>
       <c r="C59" s="2"/>
       <c r="D59" s="2"/>
@@ -1376,8 +1518,9 @@
       <c r="G59" s="2"/>
       <c r="H59" s="2"/>
       <c r="I59" s="2"/>
-    </row>
-    <row r="60" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J59" s="2"/>
+    </row>
+    <row r="60" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B60" s="2"/>
       <c r="C60" s="2"/>
       <c r="D60" s="2"/>
@@ -1386,8 +1529,9 @@
       <c r="G60" s="2"/>
       <c r="H60" s="2"/>
       <c r="I60" s="2"/>
-    </row>
-    <row r="61" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J60" s="2"/>
+    </row>
+    <row r="61" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B61" s="2"/>
       <c r="C61" s="2"/>
       <c r="D61" s="2"/>
@@ -1396,8 +1540,9 @@
       <c r="G61" s="2"/>
       <c r="H61" s="2"/>
       <c r="I61" s="2"/>
-    </row>
-    <row r="62" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J61" s="2"/>
+    </row>
+    <row r="62" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B62" s="2"/>
       <c r="C62" s="2"/>
       <c r="D62" s="2"/>
@@ -1406,8 +1551,9 @@
       <c r="G62" s="2"/>
       <c r="H62" s="2"/>
       <c r="I62" s="2"/>
-    </row>
-    <row r="63" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J62" s="2"/>
+    </row>
+    <row r="63" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B63" s="2"/>
       <c r="C63" s="2"/>
       <c r="D63" s="2"/>
@@ -1416,8 +1562,9 @@
       <c r="G63" s="2"/>
       <c r="H63" s="2"/>
       <c r="I63" s="2"/>
-    </row>
-    <row r="64" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J63" s="2"/>
+    </row>
+    <row r="64" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B64" s="2"/>
       <c r="C64" s="2"/>
       <c r="D64" s="2"/>
@@ -1426,8 +1573,9 @@
       <c r="G64" s="2"/>
       <c r="H64" s="2"/>
       <c r="I64" s="2"/>
-    </row>
-    <row r="65" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J64" s="2"/>
+    </row>
+    <row r="65" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B65" s="2"/>
       <c r="C65" s="2"/>
       <c r="D65" s="2"/>
@@ -1436,8 +1584,9 @@
       <c r="G65" s="2"/>
       <c r="H65" s="2"/>
       <c r="I65" s="2"/>
-    </row>
-    <row r="66" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J65" s="2"/>
+    </row>
+    <row r="66" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B66" s="2"/>
       <c r="C66" s="2"/>
       <c r="D66" s="2"/>
@@ -1446,8 +1595,9 @@
       <c r="G66" s="2"/>
       <c r="H66" s="2"/>
       <c r="I66" s="2"/>
-    </row>
-    <row r="67" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J66" s="2"/>
+    </row>
+    <row r="67" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B67" s="2"/>
       <c r="C67" s="2"/>
       <c r="D67" s="2"/>
@@ -1456,8 +1606,9 @@
       <c r="G67" s="2"/>
       <c r="H67" s="2"/>
       <c r="I67" s="2"/>
-    </row>
-    <row r="68" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J67" s="2"/>
+    </row>
+    <row r="68" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B68" s="2"/>
       <c r="C68" s="2"/>
       <c r="D68" s="2"/>
@@ -1466,8 +1617,9 @@
       <c r="G68" s="2"/>
       <c r="H68" s="2"/>
       <c r="I68" s="2"/>
-    </row>
-    <row r="69" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J68" s="2"/>
+    </row>
+    <row r="69" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B69" s="2"/>
       <c r="C69" s="2"/>
       <c r="D69" s="2"/>
@@ -1476,8 +1628,9 @@
       <c r="G69" s="2"/>
       <c r="H69" s="2"/>
       <c r="I69" s="2"/>
-    </row>
-    <row r="70" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J69" s="2"/>
+    </row>
+    <row r="70" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B70" s="2"/>
       <c r="C70" s="2"/>
       <c r="D70" s="2"/>
@@ -1486,8 +1639,9 @@
       <c r="G70" s="2"/>
       <c r="H70" s="2"/>
       <c r="I70" s="2"/>
-    </row>
-    <row r="71" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J70" s="2"/>
+    </row>
+    <row r="71" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B71" s="2"/>
       <c r="C71" s="2"/>
       <c r="D71" s="2"/>
@@ -1496,8 +1650,9 @@
       <c r="G71" s="2"/>
       <c r="H71" s="2"/>
       <c r="I71" s="2"/>
-    </row>
-    <row r="72" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J71" s="2"/>
+    </row>
+    <row r="72" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B72" s="2"/>
       <c r="C72" s="2"/>
       <c r="D72" s="2"/>
@@ -1506,8 +1661,9 @@
       <c r="G72" s="2"/>
       <c r="H72" s="2"/>
       <c r="I72" s="2"/>
-    </row>
-    <row r="73" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J72" s="2"/>
+    </row>
+    <row r="73" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B73" s="2"/>
       <c r="C73" s="2"/>
       <c r="D73" s="2"/>
@@ -1516,8 +1672,9 @@
       <c r="G73" s="2"/>
       <c r="H73" s="2"/>
       <c r="I73" s="2"/>
-    </row>
-    <row r="74" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J73" s="2"/>
+    </row>
+    <row r="74" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B74" s="2"/>
       <c r="C74" s="2"/>
       <c r="D74" s="2"/>
@@ -1526,8 +1683,9 @@
       <c r="G74" s="2"/>
       <c r="H74" s="2"/>
       <c r="I74" s="2"/>
-    </row>
-    <row r="75" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J74" s="2"/>
+    </row>
+    <row r="75" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B75" s="2"/>
       <c r="C75" s="2"/>
       <c r="D75" s="2"/>
@@ -1536,8 +1694,9 @@
       <c r="G75" s="2"/>
       <c r="H75" s="2"/>
       <c r="I75" s="2"/>
-    </row>
-    <row r="76" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J75" s="2"/>
+    </row>
+    <row r="76" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B76" s="2"/>
       <c r="C76" s="2"/>
       <c r="D76" s="2"/>
@@ -1546,8 +1705,9 @@
       <c r="G76" s="2"/>
       <c r="H76" s="2"/>
       <c r="I76" s="2"/>
-    </row>
-    <row r="77" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J76" s="2"/>
+    </row>
+    <row r="77" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B77" s="2"/>
       <c r="C77" s="2"/>
       <c r="D77" s="2"/>
@@ -1556,8 +1716,9 @@
       <c r="G77" s="2"/>
       <c r="H77" s="2"/>
       <c r="I77" s="2"/>
-    </row>
-    <row r="78" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J77" s="2"/>
+    </row>
+    <row r="78" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B78" s="2"/>
       <c r="C78" s="2"/>
       <c r="D78" s="2"/>
@@ -1566,8 +1727,9 @@
       <c r="G78" s="2"/>
       <c r="H78" s="2"/>
       <c r="I78" s="2"/>
-    </row>
-    <row r="79" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J78" s="2"/>
+    </row>
+    <row r="79" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B79" s="2"/>
       <c r="C79" s="2"/>
       <c r="D79" s="2"/>
@@ -1576,8 +1738,9 @@
       <c r="G79" s="2"/>
       <c r="H79" s="2"/>
       <c r="I79" s="2"/>
-    </row>
-    <row r="80" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J79" s="2"/>
+    </row>
+    <row r="80" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B80" s="2"/>
       <c r="C80" s="2"/>
       <c r="D80" s="2"/>
@@ -1586,8 +1749,9 @@
       <c r="G80" s="2"/>
       <c r="H80" s="2"/>
       <c r="I80" s="2"/>
-    </row>
-    <row r="81" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J80" s="2"/>
+    </row>
+    <row r="81" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B81" s="2"/>
       <c r="C81" s="2"/>
       <c r="D81" s="2"/>
@@ -1596,8 +1760,9 @@
       <c r="G81" s="2"/>
       <c r="H81" s="2"/>
       <c r="I81" s="2"/>
-    </row>
-    <row r="82" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J81" s="2"/>
+    </row>
+    <row r="82" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B82" s="2"/>
       <c r="C82" s="2"/>
       <c r="D82" s="2"/>
@@ -1606,8 +1771,9 @@
       <c r="G82" s="2"/>
       <c r="H82" s="2"/>
       <c r="I82" s="2"/>
-    </row>
-    <row r="83" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J82" s="2"/>
+    </row>
+    <row r="83" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B83" s="2"/>
       <c r="C83" s="2"/>
       <c r="D83" s="2"/>
@@ -1616,8 +1782,9 @@
       <c r="G83" s="2"/>
       <c r="H83" s="2"/>
       <c r="I83" s="2"/>
-    </row>
-    <row r="84" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J83" s="2"/>
+    </row>
+    <row r="84" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B84" s="2"/>
       <c r="C84" s="2"/>
       <c r="D84" s="2"/>
@@ -1626,8 +1793,9 @@
       <c r="G84" s="2"/>
       <c r="H84" s="2"/>
       <c r="I84" s="2"/>
-    </row>
-    <row r="85" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J84" s="2"/>
+    </row>
+    <row r="85" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B85" s="2"/>
       <c r="C85" s="2"/>
       <c r="D85" s="2"/>
@@ -1636,8 +1804,9 @@
       <c r="G85" s="2"/>
       <c r="H85" s="2"/>
       <c r="I85" s="2"/>
-    </row>
-    <row r="86" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J85" s="2"/>
+    </row>
+    <row r="86" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B86" s="2"/>
       <c r="C86" s="2"/>
       <c r="D86" s="2"/>
@@ -1646,8 +1815,9 @@
       <c r="G86" s="2"/>
       <c r="H86" s="2"/>
       <c r="I86" s="2"/>
-    </row>
-    <row r="87" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J86" s="2"/>
+    </row>
+    <row r="87" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B87" s="2"/>
       <c r="C87" s="2"/>
       <c r="D87" s="2"/>
@@ -1656,8 +1826,9 @@
       <c r="G87" s="2"/>
       <c r="H87" s="2"/>
       <c r="I87" s="2"/>
-    </row>
-    <row r="88" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J87" s="2"/>
+    </row>
+    <row r="88" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B88" s="2"/>
       <c r="C88" s="2"/>
       <c r="D88" s="2"/>
@@ -1666,8 +1837,9 @@
       <c r="G88" s="2"/>
       <c r="H88" s="2"/>
       <c r="I88" s="2"/>
-    </row>
-    <row r="89" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J88" s="2"/>
+    </row>
+    <row r="89" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B89" s="2"/>
       <c r="C89" s="2"/>
       <c r="D89" s="2"/>
@@ -1676,8 +1848,9 @@
       <c r="G89" s="2"/>
       <c r="H89" s="2"/>
       <c r="I89" s="2"/>
-    </row>
-    <row r="90" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J89" s="2"/>
+    </row>
+    <row r="90" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B90" s="2"/>
       <c r="C90" s="2"/>
       <c r="D90" s="2"/>
@@ -1686,8 +1859,9 @@
       <c r="G90" s="2"/>
       <c r="H90" s="2"/>
       <c r="I90" s="2"/>
-    </row>
-    <row r="91" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J90" s="2"/>
+    </row>
+    <row r="91" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B91" s="2"/>
       <c r="C91" s="2"/>
       <c r="D91" s="2"/>
@@ -1696,8 +1870,9 @@
       <c r="G91" s="2"/>
       <c r="H91" s="2"/>
       <c r="I91" s="2"/>
-    </row>
-    <row r="92" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J91" s="2"/>
+    </row>
+    <row r="92" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B92" s="2"/>
       <c r="C92" s="2"/>
       <c r="D92" s="2"/>
@@ -1706,8 +1881,9 @@
       <c r="G92" s="2"/>
       <c r="H92" s="2"/>
       <c r="I92" s="2"/>
-    </row>
-    <row r="93" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J92" s="2"/>
+    </row>
+    <row r="93" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B93" s="2"/>
       <c r="C93" s="2"/>
       <c r="D93" s="2"/>
@@ -1716,8 +1892,9 @@
       <c r="G93" s="2"/>
       <c r="H93" s="2"/>
       <c r="I93" s="2"/>
-    </row>
-    <row r="94" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J93" s="2"/>
+    </row>
+    <row r="94" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B94" s="2"/>
       <c r="C94" s="2"/>
       <c r="D94" s="2"/>
@@ -1726,8 +1903,9 @@
       <c r="G94" s="2"/>
       <c r="H94" s="2"/>
       <c r="I94" s="2"/>
-    </row>
-    <row r="95" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J94" s="2"/>
+    </row>
+    <row r="95" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B95" s="2"/>
       <c r="C95" s="2"/>
       <c r="D95" s="2"/>
@@ -1736,8 +1914,9 @@
       <c r="G95" s="2"/>
       <c r="H95" s="2"/>
       <c r="I95" s="2"/>
-    </row>
-    <row r="96" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J95" s="2"/>
+    </row>
+    <row r="96" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B96" s="2"/>
       <c r="C96" s="2"/>
       <c r="D96" s="2"/>
@@ -1746,8 +1925,9 @@
       <c r="G96" s="2"/>
       <c r="H96" s="2"/>
       <c r="I96" s="2"/>
-    </row>
-    <row r="97" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J96" s="2"/>
+    </row>
+    <row r="97" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B97" s="2"/>
       <c r="C97" s="2"/>
       <c r="D97" s="2"/>
@@ -1756,8 +1936,9 @@
       <c r="G97" s="2"/>
       <c r="H97" s="2"/>
       <c r="I97" s="2"/>
-    </row>
-    <row r="98" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J97" s="2"/>
+    </row>
+    <row r="98" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B98" s="2"/>
       <c r="C98" s="2"/>
       <c r="D98" s="2"/>
@@ -1766,8 +1947,9 @@
       <c r="G98" s="2"/>
       <c r="H98" s="2"/>
       <c r="I98" s="2"/>
-    </row>
-    <row r="99" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J98" s="2"/>
+    </row>
+    <row r="99" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B99" s="2"/>
       <c r="C99" s="2"/>
       <c r="D99" s="2"/>
@@ -1776,8 +1958,9 @@
       <c r="G99" s="2"/>
       <c r="H99" s="2"/>
       <c r="I99" s="2"/>
-    </row>
-    <row r="100" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J99" s="2"/>
+    </row>
+    <row r="100" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B100" s="2"/>
       <c r="C100" s="2"/>
       <c r="D100" s="2"/>
@@ -1786,8 +1969,9 @@
       <c r="G100" s="2"/>
       <c r="H100" s="2"/>
       <c r="I100" s="2"/>
-    </row>
-    <row r="101" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J100" s="2"/>
+    </row>
+    <row r="101" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B101" s="2"/>
       <c r="C101" s="2"/>
       <c r="D101" s="2"/>
@@ -1796,8 +1980,9 @@
       <c r="G101" s="2"/>
       <c r="H101" s="2"/>
       <c r="I101" s="2"/>
-    </row>
-    <row r="102" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J101" s="2"/>
+    </row>
+    <row r="102" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B102" s="2"/>
       <c r="C102" s="2"/>
       <c r="D102" s="2"/>
@@ -1806,8 +1991,9 @@
       <c r="G102" s="2"/>
       <c r="H102" s="2"/>
       <c r="I102" s="2"/>
-    </row>
-    <row r="103" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J102" s="2"/>
+    </row>
+    <row r="103" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B103" s="2"/>
       <c r="C103" s="2"/>
       <c r="D103" s="2"/>
@@ -1816,8 +2002,9 @@
       <c r="G103" s="2"/>
       <c r="H103" s="2"/>
       <c r="I103" s="2"/>
-    </row>
-    <row r="104" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J103" s="2"/>
+    </row>
+    <row r="104" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B104" s="2"/>
       <c r="C104" s="2"/>
       <c r="D104" s="2"/>
@@ -1826,8 +2013,9 @@
       <c r="G104" s="2"/>
       <c r="H104" s="2"/>
       <c r="I104" s="2"/>
-    </row>
-    <row r="105" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J104" s="2"/>
+    </row>
+    <row r="105" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B105" s="2"/>
       <c r="C105" s="2"/>
       <c r="D105" s="2"/>
@@ -1836,8 +2024,9 @@
       <c r="G105" s="2"/>
       <c r="H105" s="2"/>
       <c r="I105" s="2"/>
-    </row>
-    <row r="106" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J105" s="2"/>
+    </row>
+    <row r="106" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B106" s="2"/>
       <c r="C106" s="2"/>
       <c r="D106" s="2"/>
@@ -1846,8 +2035,9 @@
       <c r="G106" s="2"/>
       <c r="H106" s="2"/>
       <c r="I106" s="2"/>
-    </row>
-    <row r="107" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J106" s="2"/>
+    </row>
+    <row r="107" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B107" s="2"/>
       <c r="C107" s="2"/>
       <c r="D107" s="2"/>
@@ -1856,8 +2046,9 @@
       <c r="G107" s="2"/>
       <c r="H107" s="2"/>
       <c r="I107" s="2"/>
-    </row>
-    <row r="108" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J107" s="2"/>
+    </row>
+    <row r="108" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B108" s="2"/>
       <c r="C108" s="2"/>
       <c r="D108" s="2"/>
@@ -1866,8 +2057,9 @@
       <c r="G108" s="2"/>
       <c r="H108" s="2"/>
       <c r="I108" s="2"/>
-    </row>
-    <row r="109" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J108" s="2"/>
+    </row>
+    <row r="109" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B109" s="2"/>
       <c r="C109" s="2"/>
       <c r="D109" s="2"/>
@@ -1876,8 +2068,9 @@
       <c r="G109" s="2"/>
       <c r="H109" s="2"/>
       <c r="I109" s="2"/>
-    </row>
-    <row r="110" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J109" s="2"/>
+    </row>
+    <row r="110" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B110" s="2"/>
       <c r="C110" s="2"/>
       <c r="D110" s="2"/>
@@ -1886,8 +2079,9 @@
       <c r="G110" s="2"/>
       <c r="H110" s="2"/>
       <c r="I110" s="2"/>
-    </row>
-    <row r="111" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J110" s="2"/>
+    </row>
+    <row r="111" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B111" s="2"/>
       <c r="C111" s="2"/>
       <c r="D111" s="2"/>
@@ -1896,8 +2090,9 @@
       <c r="G111" s="2"/>
       <c r="H111" s="2"/>
       <c r="I111" s="2"/>
-    </row>
-    <row r="112" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J111" s="2"/>
+    </row>
+    <row r="112" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B112" s="2"/>
       <c r="C112" s="2"/>
       <c r="D112" s="2"/>
@@ -1906,8 +2101,9 @@
       <c r="G112" s="2"/>
       <c r="H112" s="2"/>
       <c r="I112" s="2"/>
-    </row>
-    <row r="113" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J112" s="2"/>
+    </row>
+    <row r="113" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B113" s="2"/>
       <c r="C113" s="2"/>
       <c r="D113" s="2"/>
@@ -1916,8 +2112,9 @@
       <c r="G113" s="2"/>
       <c r="H113" s="2"/>
       <c r="I113" s="2"/>
-    </row>
-    <row r="114" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J113" s="2"/>
+    </row>
+    <row r="114" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B114" s="2"/>
       <c r="C114" s="2"/>
       <c r="D114" s="2"/>
@@ -1926,8 +2123,9 @@
       <c r="G114" s="2"/>
       <c r="H114" s="2"/>
       <c r="I114" s="2"/>
-    </row>
-    <row r="115" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J114" s="2"/>
+    </row>
+    <row r="115" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B115" s="2"/>
       <c r="C115" s="2"/>
       <c r="D115" s="2"/>
@@ -1936,8 +2134,9 @@
       <c r="G115" s="2"/>
       <c r="H115" s="2"/>
       <c r="I115" s="2"/>
-    </row>
-    <row r="116" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J115" s="2"/>
+    </row>
+    <row r="116" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B116" s="2"/>
       <c r="C116" s="2"/>
       <c r="D116" s="2"/>
@@ -1946,8 +2145,9 @@
       <c r="G116" s="2"/>
       <c r="H116" s="2"/>
       <c r="I116" s="2"/>
-    </row>
-    <row r="117" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J116" s="2"/>
+    </row>
+    <row r="117" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B117" s="2"/>
       <c r="C117" s="2"/>
       <c r="D117" s="2"/>
@@ -1956,8 +2156,9 @@
       <c r="G117" s="2"/>
       <c r="H117" s="2"/>
       <c r="I117" s="2"/>
-    </row>
-    <row r="118" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J117" s="2"/>
+    </row>
+    <row r="118" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B118" s="2"/>
       <c r="C118" s="2"/>
       <c r="D118" s="2"/>
@@ -1966,8 +2167,9 @@
       <c r="G118" s="2"/>
       <c r="H118" s="2"/>
       <c r="I118" s="2"/>
-    </row>
-    <row r="119" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J118" s="2"/>
+    </row>
+    <row r="119" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B119" s="2"/>
       <c r="C119" s="2"/>
       <c r="D119" s="2"/>
@@ -1976,8 +2178,9 @@
       <c r="G119" s="2"/>
       <c r="H119" s="2"/>
       <c r="I119" s="2"/>
-    </row>
-    <row r="120" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J119" s="2"/>
+    </row>
+    <row r="120" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B120" s="2"/>
       <c r="C120" s="2"/>
       <c r="D120" s="2"/>
@@ -1986,8 +2189,9 @@
       <c r="G120" s="2"/>
       <c r="H120" s="2"/>
       <c r="I120" s="2"/>
-    </row>
-    <row r="121" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J120" s="2"/>
+    </row>
+    <row r="121" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B121" s="2"/>
       <c r="C121" s="2"/>
       <c r="D121" s="2"/>
@@ -1996,8 +2200,9 @@
       <c r="G121" s="2"/>
       <c r="H121" s="2"/>
       <c r="I121" s="2"/>
-    </row>
-    <row r="122" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J121" s="2"/>
+    </row>
+    <row r="122" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B122" s="2"/>
       <c r="C122" s="2"/>
       <c r="D122" s="2"/>
@@ -2006,8 +2211,9 @@
       <c r="G122" s="2"/>
       <c r="H122" s="2"/>
       <c r="I122" s="2"/>
-    </row>
-    <row r="123" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J122" s="2"/>
+    </row>
+    <row r="123" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B123" s="2"/>
       <c r="C123" s="2"/>
       <c r="D123" s="2"/>
@@ -2016,8 +2222,9 @@
       <c r="G123" s="2"/>
       <c r="H123" s="2"/>
       <c r="I123" s="2"/>
-    </row>
-    <row r="124" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J123" s="2"/>
+    </row>
+    <row r="124" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B124" s="2"/>
       <c r="C124" s="2"/>
       <c r="D124" s="2"/>
@@ -2026,8 +2233,9 @@
       <c r="G124" s="2"/>
       <c r="H124" s="2"/>
       <c r="I124" s="2"/>
-    </row>
-    <row r="125" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J124" s="2"/>
+    </row>
+    <row r="125" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B125" s="2"/>
       <c r="C125" s="2"/>
       <c r="D125" s="2"/>
@@ -2036,8 +2244,9 @@
       <c r="G125" s="2"/>
       <c r="H125" s="2"/>
       <c r="I125" s="2"/>
-    </row>
-    <row r="126" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J125" s="2"/>
+    </row>
+    <row r="126" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B126" s="2"/>
       <c r="C126" s="2"/>
       <c r="D126" s="2"/>
@@ -2046,8 +2255,9 @@
       <c r="G126" s="2"/>
       <c r="H126" s="2"/>
       <c r="I126" s="2"/>
-    </row>
-    <row r="127" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J126" s="2"/>
+    </row>
+    <row r="127" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B127" s="2"/>
       <c r="C127" s="2"/>
       <c r="D127" s="2"/>
@@ -2056,8 +2266,9 @@
       <c r="G127" s="2"/>
       <c r="H127" s="2"/>
       <c r="I127" s="2"/>
-    </row>
-    <row r="128" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J127" s="2"/>
+    </row>
+    <row r="128" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B128" s="2"/>
       <c r="C128" s="2"/>
       <c r="D128" s="2"/>
@@ -2066,8 +2277,9 @@
       <c r="G128" s="2"/>
       <c r="H128" s="2"/>
       <c r="I128" s="2"/>
-    </row>
-    <row r="129" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J128" s="2"/>
+    </row>
+    <row r="129" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B129" s="2"/>
       <c r="C129" s="2"/>
       <c r="D129" s="2"/>
@@ -2076,8 +2288,9 @@
       <c r="G129" s="2"/>
       <c r="H129" s="2"/>
       <c r="I129" s="2"/>
-    </row>
-    <row r="130" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J129" s="2"/>
+    </row>
+    <row r="130" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B130" s="2"/>
       <c r="C130" s="2"/>
       <c r="D130" s="2"/>
@@ -2086,8 +2299,9 @@
       <c r="G130" s="2"/>
       <c r="H130" s="2"/>
       <c r="I130" s="2"/>
-    </row>
-    <row r="131" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J130" s="2"/>
+    </row>
+    <row r="131" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B131" s="2"/>
       <c r="C131" s="2"/>
       <c r="D131" s="2"/>
@@ -2096,8 +2310,9 @@
       <c r="G131" s="2"/>
       <c r="H131" s="2"/>
       <c r="I131" s="2"/>
-    </row>
-    <row r="132" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J131" s="2"/>
+    </row>
+    <row r="132" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B132" s="2"/>
       <c r="C132" s="2"/>
       <c r="D132" s="2"/>
@@ -2106,8 +2321,9 @@
       <c r="G132" s="2"/>
       <c r="H132" s="2"/>
       <c r="I132" s="2"/>
-    </row>
-    <row r="133" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J132" s="2"/>
+    </row>
+    <row r="133" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B133" s="2"/>
       <c r="C133" s="2"/>
       <c r="D133" s="2"/>
@@ -2116,8 +2332,9 @@
       <c r="G133" s="2"/>
       <c r="H133" s="2"/>
       <c r="I133" s="2"/>
-    </row>
-    <row r="134" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J133" s="2"/>
+    </row>
+    <row r="134" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B134" s="2"/>
       <c r="C134" s="2"/>
       <c r="D134" s="2"/>
@@ -2126,8 +2343,9 @@
       <c r="G134" s="2"/>
       <c r="H134" s="2"/>
       <c r="I134" s="2"/>
-    </row>
-    <row r="135" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J134" s="2"/>
+    </row>
+    <row r="135" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B135" s="2"/>
       <c r="C135" s="2"/>
       <c r="D135" s="2"/>
@@ -2136,8 +2354,9 @@
       <c r="G135" s="2"/>
       <c r="H135" s="2"/>
       <c r="I135" s="2"/>
-    </row>
-    <row r="136" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J135" s="2"/>
+    </row>
+    <row r="136" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B136" s="2"/>
       <c r="C136" s="2"/>
       <c r="D136" s="2"/>
@@ -2146,8 +2365,9 @@
       <c r="G136" s="2"/>
       <c r="H136" s="2"/>
       <c r="I136" s="2"/>
-    </row>
-    <row r="137" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J136" s="2"/>
+    </row>
+    <row r="137" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B137" s="2"/>
       <c r="C137" s="2"/>
       <c r="D137" s="2"/>
@@ -2156,8 +2376,9 @@
       <c r="G137" s="2"/>
       <c r="H137" s="2"/>
       <c r="I137" s="2"/>
-    </row>
-    <row r="138" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J137" s="2"/>
+    </row>
+    <row r="138" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B138" s="2"/>
       <c r="C138" s="2"/>
       <c r="D138" s="2"/>
@@ -2166,8 +2387,9 @@
       <c r="G138" s="2"/>
       <c r="H138" s="2"/>
       <c r="I138" s="2"/>
-    </row>
-    <row r="139" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J138" s="2"/>
+    </row>
+    <row r="139" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B139" s="2"/>
       <c r="C139" s="2"/>
       <c r="D139" s="2"/>
@@ -2176,8 +2398,9 @@
       <c r="G139" s="2"/>
       <c r="H139" s="2"/>
       <c r="I139" s="2"/>
-    </row>
-    <row r="140" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J139" s="2"/>
+    </row>
+    <row r="140" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B140" s="2"/>
       <c r="C140" s="2"/>
       <c r="D140" s="2"/>
@@ -2186,8 +2409,9 @@
       <c r="G140" s="2"/>
       <c r="H140" s="2"/>
       <c r="I140" s="2"/>
-    </row>
-    <row r="141" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J140" s="2"/>
+    </row>
+    <row r="141" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B141" s="2"/>
       <c r="C141" s="2"/>
       <c r="D141" s="2"/>
@@ -2196,8 +2420,9 @@
       <c r="G141" s="2"/>
       <c r="H141" s="2"/>
       <c r="I141" s="2"/>
-    </row>
-    <row r="142" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J141" s="2"/>
+    </row>
+    <row r="142" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B142" s="2"/>
       <c r="C142" s="2"/>
       <c r="D142" s="2"/>
@@ -2206,8 +2431,9 @@
       <c r="G142" s="2"/>
       <c r="H142" s="2"/>
       <c r="I142" s="2"/>
-    </row>
-    <row r="143" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J142" s="2"/>
+    </row>
+    <row r="143" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B143" s="2"/>
       <c r="C143" s="2"/>
       <c r="D143" s="2"/>
@@ -2216,8 +2442,9 @@
       <c r="G143" s="2"/>
       <c r="H143" s="2"/>
       <c r="I143" s="2"/>
-    </row>
-    <row r="144" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J143" s="2"/>
+    </row>
+    <row r="144" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B144" s="2"/>
       <c r="C144" s="2"/>
       <c r="D144" s="2"/>
@@ -2226,8 +2453,9 @@
       <c r="G144" s="2"/>
       <c r="H144" s="2"/>
       <c r="I144" s="2"/>
-    </row>
-    <row r="145" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J144" s="2"/>
+    </row>
+    <row r="145" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B145" s="2"/>
       <c r="C145" s="2"/>
       <c r="D145" s="2"/>
@@ -2236,8 +2464,9 @@
       <c r="G145" s="2"/>
       <c r="H145" s="2"/>
       <c r="I145" s="2"/>
-    </row>
-    <row r="146" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J145" s="2"/>
+    </row>
+    <row r="146" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B146" s="2"/>
       <c r="C146" s="2"/>
       <c r="D146" s="2"/>
@@ -2246,8 +2475,9 @@
       <c r="G146" s="2"/>
       <c r="H146" s="2"/>
       <c r="I146" s="2"/>
-    </row>
-    <row r="147" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J146" s="2"/>
+    </row>
+    <row r="147" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B147" s="2"/>
       <c r="C147" s="2"/>
       <c r="D147" s="2"/>
@@ -2256,8 +2486,9 @@
       <c r="G147" s="2"/>
       <c r="H147" s="2"/>
       <c r="I147" s="2"/>
-    </row>
-    <row r="148" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J147" s="2"/>
+    </row>
+    <row r="148" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B148" s="2"/>
       <c r="C148" s="2"/>
       <c r="D148" s="2"/>
@@ -2266,8 +2497,9 @@
       <c r="G148" s="2"/>
       <c r="H148" s="2"/>
       <c r="I148" s="2"/>
-    </row>
-    <row r="149" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J148" s="2"/>
+    </row>
+    <row r="149" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B149" s="2"/>
       <c r="C149" s="2"/>
       <c r="D149" s="2"/>
@@ -2276,8 +2508,9 @@
       <c r="G149" s="2"/>
       <c r="H149" s="2"/>
       <c r="I149" s="2"/>
-    </row>
-    <row r="150" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J149" s="2"/>
+    </row>
+    <row r="150" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B150" s="2"/>
       <c r="C150" s="2"/>
       <c r="D150" s="2"/>
@@ -2286,8 +2519,9 @@
       <c r="G150" s="2"/>
       <c r="H150" s="2"/>
       <c r="I150" s="2"/>
-    </row>
-    <row r="151" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J150" s="2"/>
+    </row>
+    <row r="151" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B151" s="2"/>
       <c r="C151" s="2"/>
       <c r="D151" s="2"/>
@@ -2296,8 +2530,9 @@
       <c r="G151" s="2"/>
       <c r="H151" s="2"/>
       <c r="I151" s="2"/>
-    </row>
-    <row r="152" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J151" s="2"/>
+    </row>
+    <row r="152" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B152" s="2"/>
       <c r="C152" s="2"/>
       <c r="D152" s="2"/>
@@ -2306,8 +2541,9 @@
       <c r="G152" s="2"/>
       <c r="H152" s="2"/>
       <c r="I152" s="2"/>
-    </row>
-    <row r="153" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J152" s="2"/>
+    </row>
+    <row r="153" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B153" s="2"/>
       <c r="C153" s="2"/>
       <c r="D153" s="2"/>
@@ -2316,8 +2552,9 @@
       <c r="G153" s="2"/>
       <c r="H153" s="2"/>
       <c r="I153" s="2"/>
-    </row>
-    <row r="154" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J153" s="2"/>
+    </row>
+    <row r="154" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B154" s="2"/>
       <c r="C154" s="2"/>
       <c r="D154" s="2"/>
@@ -2326,8 +2563,9 @@
       <c r="G154" s="2"/>
       <c r="H154" s="2"/>
       <c r="I154" s="2"/>
-    </row>
-    <row r="155" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J154" s="2"/>
+    </row>
+    <row r="155" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B155" s="2"/>
       <c r="C155" s="2"/>
       <c r="D155" s="2"/>
@@ -2336,8 +2574,9 @@
       <c r="G155" s="2"/>
       <c r="H155" s="2"/>
       <c r="I155" s="2"/>
-    </row>
-    <row r="156" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J155" s="2"/>
+    </row>
+    <row r="156" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B156" s="2"/>
       <c r="C156" s="2"/>
       <c r="D156" s="2"/>
@@ -2346,8 +2585,9 @@
       <c r="G156" s="2"/>
       <c r="H156" s="2"/>
       <c r="I156" s="2"/>
-    </row>
-    <row r="157" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J156" s="2"/>
+    </row>
+    <row r="157" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B157" s="2"/>
       <c r="C157" s="2"/>
       <c r="D157" s="2"/>
@@ -2356,8 +2596,9 @@
       <c r="G157" s="2"/>
       <c r="H157" s="2"/>
       <c r="I157" s="2"/>
-    </row>
-    <row r="158" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J157" s="2"/>
+    </row>
+    <row r="158" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B158" s="2"/>
       <c r="C158" s="2"/>
       <c r="D158" s="2"/>
@@ -2366,8 +2607,9 @@
       <c r="G158" s="2"/>
       <c r="H158" s="2"/>
       <c r="I158" s="2"/>
-    </row>
-    <row r="159" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J158" s="2"/>
+    </row>
+    <row r="159" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B159" s="2"/>
       <c r="C159" s="2"/>
       <c r="D159" s="2"/>
@@ -2376,8 +2618,9 @@
       <c r="G159" s="2"/>
       <c r="H159" s="2"/>
       <c r="I159" s="2"/>
-    </row>
-    <row r="160" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J159" s="2"/>
+    </row>
+    <row r="160" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B160" s="2"/>
       <c r="C160" s="2"/>
       <c r="D160" s="2"/>
@@ -2386,8 +2629,9 @@
       <c r="G160" s="2"/>
       <c r="H160" s="2"/>
       <c r="I160" s="2"/>
-    </row>
-    <row r="161" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J160" s="2"/>
+    </row>
+    <row r="161" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B161" s="2"/>
       <c r="C161" s="2"/>
       <c r="D161" s="2"/>
@@ -2396,8 +2640,9 @@
       <c r="G161" s="2"/>
       <c r="H161" s="2"/>
       <c r="I161" s="2"/>
-    </row>
-    <row r="162" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J161" s="2"/>
+    </row>
+    <row r="162" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B162" s="2"/>
       <c r="C162" s="2"/>
       <c r="D162" s="2"/>
@@ -2406,8 +2651,9 @@
       <c r="G162" s="2"/>
       <c r="H162" s="2"/>
       <c r="I162" s="2"/>
-    </row>
-    <row r="163" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J162" s="2"/>
+    </row>
+    <row r="163" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B163" s="2"/>
       <c r="C163" s="2"/>
       <c r="D163" s="2"/>
@@ -2416,8 +2662,9 @@
       <c r="G163" s="2"/>
       <c r="H163" s="2"/>
       <c r="I163" s="2"/>
-    </row>
-    <row r="164" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J163" s="2"/>
+    </row>
+    <row r="164" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B164" s="2"/>
       <c r="C164" s="2"/>
       <c r="D164" s="2"/>
@@ -2426,8 +2673,9 @@
       <c r="G164" s="2"/>
       <c r="H164" s="2"/>
       <c r="I164" s="2"/>
-    </row>
-    <row r="165" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J164" s="2"/>
+    </row>
+    <row r="165" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B165" s="2"/>
       <c r="C165" s="2"/>
       <c r="D165" s="2"/>
@@ -2436,8 +2684,9 @@
       <c r="G165" s="2"/>
       <c r="H165" s="2"/>
       <c r="I165" s="2"/>
-    </row>
-    <row r="166" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J165" s="2"/>
+    </row>
+    <row r="166" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B166" s="2"/>
       <c r="C166" s="2"/>
       <c r="D166" s="2"/>
@@ -2446,8 +2695,9 @@
       <c r="G166" s="2"/>
       <c r="H166" s="2"/>
       <c r="I166" s="2"/>
-    </row>
-    <row r="167" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J166" s="2"/>
+    </row>
+    <row r="167" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B167" s="2"/>
       <c r="C167" s="2"/>
       <c r="D167" s="2"/>
@@ -2456,8 +2706,9 @@
       <c r="G167" s="2"/>
       <c r="H167" s="2"/>
       <c r="I167" s="2"/>
-    </row>
-    <row r="168" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J167" s="2"/>
+    </row>
+    <row r="168" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B168" s="2"/>
       <c r="C168" s="2"/>
       <c r="D168" s="2"/>
@@ -2466,8 +2717,9 @@
       <c r="G168" s="2"/>
       <c r="H168" s="2"/>
       <c r="I168" s="2"/>
-    </row>
-    <row r="169" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J168" s="2"/>
+    </row>
+    <row r="169" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B169" s="2"/>
       <c r="C169" s="2"/>
       <c r="D169" s="2"/>
@@ -2476,8 +2728,9 @@
       <c r="G169" s="2"/>
       <c r="H169" s="2"/>
       <c r="I169" s="2"/>
-    </row>
-    <row r="170" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J169" s="2"/>
+    </row>
+    <row r="170" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B170" s="2"/>
       <c r="C170" s="2"/>
       <c r="D170" s="2"/>
@@ -2486,8 +2739,9 @@
       <c r="G170" s="2"/>
       <c r="H170" s="2"/>
       <c r="I170" s="2"/>
-    </row>
-    <row r="171" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J170" s="2"/>
+    </row>
+    <row r="171" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B171" s="2"/>
       <c r="C171" s="2"/>
       <c r="D171" s="2"/>
@@ -2496,8 +2750,9 @@
       <c r="G171" s="2"/>
       <c r="H171" s="2"/>
       <c r="I171" s="2"/>
-    </row>
-    <row r="172" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J171" s="2"/>
+    </row>
+    <row r="172" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B172" s="2"/>
       <c r="C172" s="2"/>
       <c r="D172" s="2"/>
@@ -2506,8 +2761,9 @@
       <c r="G172" s="2"/>
       <c r="H172" s="2"/>
       <c r="I172" s="2"/>
-    </row>
-    <row r="173" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J172" s="2"/>
+    </row>
+    <row r="173" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B173" s="2"/>
       <c r="C173" s="2"/>
       <c r="D173" s="2"/>
@@ -2516,8 +2772,9 @@
       <c r="G173" s="2"/>
       <c r="H173" s="2"/>
       <c r="I173" s="2"/>
-    </row>
-    <row r="174" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J173" s="2"/>
+    </row>
+    <row r="174" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B174" s="2"/>
       <c r="C174" s="2"/>
       <c r="D174" s="2"/>
@@ -2526,8 +2783,9 @@
       <c r="G174" s="2"/>
       <c r="H174" s="2"/>
       <c r="I174" s="2"/>
-    </row>
-    <row r="175" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J174" s="2"/>
+    </row>
+    <row r="175" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B175" s="2"/>
       <c r="C175" s="2"/>
       <c r="D175" s="2"/>
@@ -2536,8 +2794,9 @@
       <c r="G175" s="2"/>
       <c r="H175" s="2"/>
       <c r="I175" s="2"/>
-    </row>
-    <row r="176" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J175" s="2"/>
+    </row>
+    <row r="176" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B176" s="2"/>
       <c r="C176" s="2"/>
       <c r="D176" s="2"/>
@@ -2546,8 +2805,9 @@
       <c r="G176" s="2"/>
       <c r="H176" s="2"/>
       <c r="I176" s="2"/>
-    </row>
-    <row r="177" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J176" s="2"/>
+    </row>
+    <row r="177" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B177" s="2"/>
       <c r="C177" s="2"/>
       <c r="D177" s="2"/>
@@ -2556,8 +2816,9 @@
       <c r="G177" s="2"/>
       <c r="H177" s="2"/>
       <c r="I177" s="2"/>
-    </row>
-    <row r="178" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J177" s="2"/>
+    </row>
+    <row r="178" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B178" s="2"/>
       <c r="C178" s="2"/>
       <c r="D178" s="2"/>
@@ -2566,8 +2827,9 @@
       <c r="G178" s="2"/>
       <c r="H178" s="2"/>
       <c r="I178" s="2"/>
-    </row>
-    <row r="179" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J178" s="2"/>
+    </row>
+    <row r="179" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B179" s="2"/>
       <c r="C179" s="2"/>
       <c r="D179" s="2"/>
@@ -2576,8 +2838,9 @@
       <c r="G179" s="2"/>
       <c r="H179" s="2"/>
       <c r="I179" s="2"/>
-    </row>
-    <row r="180" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J179" s="2"/>
+    </row>
+    <row r="180" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B180" s="2"/>
       <c r="C180" s="2"/>
       <c r="D180" s="2"/>
@@ -2586,8 +2849,9 @@
       <c r="G180" s="2"/>
       <c r="H180" s="2"/>
       <c r="I180" s="2"/>
-    </row>
-    <row r="181" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J180" s="2"/>
+    </row>
+    <row r="181" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B181" s="2"/>
       <c r="C181" s="2"/>
       <c r="D181" s="2"/>
@@ -2596,8 +2860,9 @@
       <c r="G181" s="2"/>
       <c r="H181" s="2"/>
       <c r="I181" s="2"/>
-    </row>
-    <row r="182" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J181" s="2"/>
+    </row>
+    <row r="182" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B182" s="2"/>
       <c r="C182" s="2"/>
       <c r="D182" s="2"/>
@@ -2606,8 +2871,9 @@
       <c r="G182" s="2"/>
       <c r="H182" s="2"/>
       <c r="I182" s="2"/>
-    </row>
-    <row r="183" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J182" s="2"/>
+    </row>
+    <row r="183" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B183" s="2"/>
       <c r="C183" s="2"/>
       <c r="D183" s="2"/>
@@ -2616,8 +2882,9 @@
       <c r="G183" s="2"/>
       <c r="H183" s="2"/>
       <c r="I183" s="2"/>
-    </row>
-    <row r="184" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J183" s="2"/>
+    </row>
+    <row r="184" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B184" s="2"/>
       <c r="C184" s="2"/>
       <c r="D184" s="2"/>
@@ -2626,8 +2893,9 @@
       <c r="G184" s="2"/>
       <c r="H184" s="2"/>
       <c r="I184" s="2"/>
-    </row>
-    <row r="185" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J184" s="2"/>
+    </row>
+    <row r="185" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B185" s="2"/>
       <c r="C185" s="2"/>
       <c r="D185" s="2"/>
@@ -2636,8 +2904,9 @@
       <c r="G185" s="2"/>
       <c r="H185" s="2"/>
       <c r="I185" s="2"/>
-    </row>
-    <row r="186" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J185" s="2"/>
+    </row>
+    <row r="186" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B186" s="2"/>
       <c r="C186" s="2"/>
       <c r="D186" s="2"/>
@@ -2646,8 +2915,9 @@
       <c r="G186" s="2"/>
       <c r="H186" s="2"/>
       <c r="I186" s="2"/>
-    </row>
-    <row r="187" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J186" s="2"/>
+    </row>
+    <row r="187" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B187" s="2"/>
       <c r="C187" s="2"/>
       <c r="D187" s="2"/>
@@ -2656,8 +2926,9 @@
       <c r="G187" s="2"/>
       <c r="H187" s="2"/>
       <c r="I187" s="2"/>
-    </row>
-    <row r="188" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J187" s="2"/>
+    </row>
+    <row r="188" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B188" s="2"/>
       <c r="C188" s="2"/>
       <c r="D188" s="2"/>
@@ -2666,8 +2937,9 @@
       <c r="G188" s="2"/>
       <c r="H188" s="2"/>
       <c r="I188" s="2"/>
-    </row>
-    <row r="189" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J188" s="2"/>
+    </row>
+    <row r="189" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B189" s="2"/>
       <c r="C189" s="2"/>
       <c r="D189" s="2"/>
@@ -2676,8 +2948,9 @@
       <c r="G189" s="2"/>
       <c r="H189" s="2"/>
       <c r="I189" s="2"/>
-    </row>
-    <row r="190" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J189" s="2"/>
+    </row>
+    <row r="190" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B190" s="2"/>
       <c r="C190" s="2"/>
       <c r="D190" s="2"/>
@@ -2686,8 +2959,9 @@
       <c r="G190" s="2"/>
       <c r="H190" s="2"/>
       <c r="I190" s="2"/>
-    </row>
-    <row r="191" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J190" s="2"/>
+    </row>
+    <row r="191" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B191" s="2"/>
       <c r="C191" s="2"/>
       <c r="D191" s="2"/>
@@ -2696,8 +2970,9 @@
       <c r="G191" s="2"/>
       <c r="H191" s="2"/>
       <c r="I191" s="2"/>
-    </row>
-    <row r="192" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J191" s="2"/>
+    </row>
+    <row r="192" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B192" s="2"/>
       <c r="C192" s="2"/>
       <c r="D192" s="2"/>
@@ -2706,8 +2981,9 @@
       <c r="G192" s="2"/>
       <c r="H192" s="2"/>
       <c r="I192" s="2"/>
-    </row>
-    <row r="193" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J192" s="2"/>
+    </row>
+    <row r="193" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B193" s="2"/>
       <c r="C193" s="2"/>
       <c r="D193" s="2"/>
@@ -2716,8 +2992,9 @@
       <c r="G193" s="2"/>
       <c r="H193" s="2"/>
       <c r="I193" s="2"/>
-    </row>
-    <row r="194" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J193" s="2"/>
+    </row>
+    <row r="194" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B194" s="2"/>
       <c r="C194" s="2"/>
       <c r="D194" s="2"/>
@@ -2726,8 +3003,9 @@
       <c r="G194" s="2"/>
       <c r="H194" s="2"/>
       <c r="I194" s="2"/>
-    </row>
-    <row r="195" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J194" s="2"/>
+    </row>
+    <row r="195" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B195" s="2"/>
       <c r="C195" s="2"/>
       <c r="D195" s="2"/>
@@ -2736,8 +3014,9 @@
       <c r="G195" s="2"/>
       <c r="H195" s="2"/>
       <c r="I195" s="2"/>
-    </row>
-    <row r="196" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J195" s="2"/>
+    </row>
+    <row r="196" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B196" s="2"/>
       <c r="C196" s="2"/>
       <c r="D196" s="2"/>
@@ -2746,8 +3025,9 @@
       <c r="G196" s="2"/>
       <c r="H196" s="2"/>
       <c r="I196" s="2"/>
-    </row>
-    <row r="197" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J196" s="2"/>
+    </row>
+    <row r="197" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B197" s="2"/>
       <c r="C197" s="2"/>
       <c r="D197" s="2"/>
@@ -2756,8 +3036,9 @@
       <c r="G197" s="2"/>
       <c r="H197" s="2"/>
       <c r="I197" s="2"/>
-    </row>
-    <row r="198" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J197" s="2"/>
+    </row>
+    <row r="198" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B198" s="2"/>
       <c r="C198" s="2"/>
       <c r="D198" s="2"/>
@@ -2766,8 +3047,9 @@
       <c r="G198" s="2"/>
       <c r="H198" s="2"/>
       <c r="I198" s="2"/>
-    </row>
-    <row r="199" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J198" s="2"/>
+    </row>
+    <row r="199" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B199" s="2"/>
       <c r="C199" s="2"/>
       <c r="D199" s="2"/>
@@ -2776,8 +3058,9 @@
       <c r="G199" s="2"/>
       <c r="H199" s="2"/>
       <c r="I199" s="2"/>
-    </row>
-    <row r="200" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J199" s="2"/>
+    </row>
+    <row r="200" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B200" s="2"/>
       <c r="C200" s="2"/>
       <c r="D200" s="2"/>
@@ -2786,8 +3069,9 @@
       <c r="G200" s="2"/>
       <c r="H200" s="2"/>
       <c r="I200" s="2"/>
-    </row>
-    <row r="201" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J200" s="2"/>
+    </row>
+    <row r="201" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B201" s="2"/>
       <c r="C201" s="2"/>
       <c r="D201" s="2"/>
@@ -2796,8 +3080,9 @@
       <c r="G201" s="2"/>
       <c r="H201" s="2"/>
       <c r="I201" s="2"/>
-    </row>
-    <row r="202" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J201" s="2"/>
+    </row>
+    <row r="202" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B202" s="2"/>
       <c r="C202" s="2"/>
       <c r="D202" s="2"/>
@@ -2806,8 +3091,9 @@
       <c r="G202" s="2"/>
       <c r="H202" s="2"/>
       <c r="I202" s="2"/>
-    </row>
-    <row r="203" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J202" s="2"/>
+    </row>
+    <row r="203" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B203" s="2"/>
       <c r="C203" s="2"/>
       <c r="D203" s="2"/>
@@ -2816,8 +3102,9 @@
       <c r="G203" s="2"/>
       <c r="H203" s="2"/>
       <c r="I203" s="2"/>
-    </row>
-    <row r="204" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J203" s="2"/>
+    </row>
+    <row r="204" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B204" s="2"/>
       <c r="C204" s="2"/>
       <c r="D204" s="2"/>
@@ -2826,8 +3113,9 @@
       <c r="G204" s="2"/>
       <c r="H204" s="2"/>
       <c r="I204" s="2"/>
-    </row>
-    <row r="205" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J204" s="2"/>
+    </row>
+    <row r="205" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B205" s="2"/>
       <c r="C205" s="2"/>
       <c r="D205" s="2"/>
@@ -2836,8 +3124,9 @@
       <c r="G205" s="2"/>
       <c r="H205" s="2"/>
       <c r="I205" s="2"/>
-    </row>
-    <row r="206" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J205" s="2"/>
+    </row>
+    <row r="206" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B206" s="2"/>
       <c r="C206" s="2"/>
       <c r="D206" s="2"/>
@@ -2846,8 +3135,9 @@
       <c r="G206" s="2"/>
       <c r="H206" s="2"/>
       <c r="I206" s="2"/>
-    </row>
-    <row r="207" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J206" s="2"/>
+    </row>
+    <row r="207" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B207" s="2"/>
       <c r="C207" s="2"/>
       <c r="D207" s="2"/>
@@ -2856,8 +3146,9 @@
       <c r="G207" s="2"/>
       <c r="H207" s="2"/>
       <c r="I207" s="2"/>
-    </row>
-    <row r="208" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J207" s="2"/>
+    </row>
+    <row r="208" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B208" s="2"/>
       <c r="C208" s="2"/>
       <c r="D208" s="2"/>
@@ -2866,8 +3157,9 @@
       <c r="G208" s="2"/>
       <c r="H208" s="2"/>
       <c r="I208" s="2"/>
-    </row>
-    <row r="209" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J208" s="2"/>
+    </row>
+    <row r="209" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B209" s="2"/>
       <c r="C209" s="2"/>
       <c r="D209" s="2"/>
@@ -2876,8 +3168,9 @@
       <c r="G209" s="2"/>
       <c r="H209" s="2"/>
       <c r="I209" s="2"/>
-    </row>
-    <row r="210" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J209" s="2"/>
+    </row>
+    <row r="210" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B210" s="2"/>
       <c r="C210" s="2"/>
       <c r="D210" s="2"/>
@@ -2886,8 +3179,9 @@
       <c r="G210" s="2"/>
       <c r="H210" s="2"/>
       <c r="I210" s="2"/>
-    </row>
-    <row r="211" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J210" s="2"/>
+    </row>
+    <row r="211" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B211" s="2"/>
       <c r="C211" s="2"/>
       <c r="D211" s="2"/>
@@ -2896,8 +3190,9 @@
       <c r="G211" s="2"/>
       <c r="H211" s="2"/>
       <c r="I211" s="2"/>
-    </row>
-    <row r="212" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J211" s="2"/>
+    </row>
+    <row r="212" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B212" s="2"/>
       <c r="C212" s="2"/>
       <c r="D212" s="2"/>
@@ -2906,8 +3201,9 @@
       <c r="G212" s="2"/>
       <c r="H212" s="2"/>
       <c r="I212" s="2"/>
-    </row>
-    <row r="213" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J212" s="2"/>
+    </row>
+    <row r="213" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B213" s="2"/>
       <c r="C213" s="2"/>
       <c r="D213" s="2"/>
@@ -2916,8 +3212,9 @@
       <c r="G213" s="2"/>
       <c r="H213" s="2"/>
       <c r="I213" s="2"/>
-    </row>
-    <row r="214" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J213" s="2"/>
+    </row>
+    <row r="214" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B214" s="2"/>
       <c r="C214" s="2"/>
       <c r="D214" s="2"/>
@@ -2926,8 +3223,9 @@
       <c r="G214" s="2"/>
       <c r="H214" s="2"/>
       <c r="I214" s="2"/>
-    </row>
-    <row r="215" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J214" s="2"/>
+    </row>
+    <row r="215" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B215" s="2"/>
       <c r="C215" s="2"/>
       <c r="D215" s="2"/>
@@ -2936,8 +3234,9 @@
       <c r="G215" s="2"/>
       <c r="H215" s="2"/>
       <c r="I215" s="2"/>
-    </row>
-    <row r="216" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J215" s="2"/>
+    </row>
+    <row r="216" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B216" s="2"/>
       <c r="C216" s="2"/>
       <c r="D216" s="2"/>
@@ -2946,8 +3245,9 @@
       <c r="G216" s="2"/>
       <c r="H216" s="2"/>
       <c r="I216" s="2"/>
-    </row>
-    <row r="217" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J216" s="2"/>
+    </row>
+    <row r="217" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B217" s="2"/>
       <c r="C217" s="2"/>
       <c r="D217" s="2"/>
@@ -2956,8 +3256,9 @@
       <c r="G217" s="2"/>
       <c r="H217" s="2"/>
       <c r="I217" s="2"/>
-    </row>
-    <row r="218" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J217" s="2"/>
+    </row>
+    <row r="218" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B218" s="2"/>
       <c r="C218" s="2"/>
       <c r="D218" s="2"/>
@@ -2966,8 +3267,9 @@
       <c r="G218" s="2"/>
       <c r="H218" s="2"/>
       <c r="I218" s="2"/>
-    </row>
-    <row r="219" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J218" s="2"/>
+    </row>
+    <row r="219" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B219" s="2"/>
       <c r="C219" s="2"/>
       <c r="D219" s="2"/>
@@ -2976,8 +3278,9 @@
       <c r="G219" s="2"/>
       <c r="H219" s="2"/>
       <c r="I219" s="2"/>
-    </row>
-    <row r="220" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J219" s="2"/>
+    </row>
+    <row r="220" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B220" s="2"/>
       <c r="C220" s="2"/>
       <c r="D220" s="2"/>
@@ -2986,8 +3289,9 @@
       <c r="G220" s="2"/>
       <c r="H220" s="2"/>
       <c r="I220" s="2"/>
-    </row>
-    <row r="221" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J220" s="2"/>
+    </row>
+    <row r="221" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B221" s="2"/>
       <c r="C221" s="2"/>
       <c r="D221" s="2"/>
@@ -2996,11 +3300,42 @@
       <c r="G221" s="2"/>
       <c r="H221" s="2"/>
       <c r="I221" s="2"/>
+      <c r="J221" s="2"/>
+    </row>
+    <row r="222" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B222" s="2"/>
+      <c r="C222" s="2"/>
+      <c r="D222" s="2"/>
+      <c r="E222" s="2"/>
+      <c r="F222" s="2"/>
+      <c r="G222" s="2"/>
+      <c r="H222" s="2"/>
+      <c r="I222" s="2"/>
+      <c r="J222" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B6:I7"/>
+  <mergeCells count="9">
+    <mergeCell ref="B6:J7"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="I8:I9"/>
+    <mergeCell ref="J8:J9"/>
+    <mergeCell ref="C8:D8"/>
   </mergeCells>
+  <conditionalFormatting sqref="D10:D49">
+    <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
+      <formula>"Pago"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="2" operator="equal">
+      <formula>"Sem Direito"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
+      <formula>"Pendente"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="65" orientation="landscape" r:id="rId1"/>
   <drawing r:id="rId2"/>
@@ -3008,9 +3343,9 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="2" operator="containsText" id="{1C273855-0DFC-4DED-8EB7-87955D5053D8}">
-            <xm:f>NOT(ISERROR(SEARCH("SIM",C9)))</xm:f>
-            <xm:f>"SIM"</xm:f>
+          <x14:cfRule type="containsText" priority="5" operator="containsText" id="{761CD187-0092-47F8-B02D-8C36014B61AA}">
+            <xm:f>NOT(ISERROR(SEARCH("Com Direito",C10)))</xm:f>
+            <xm:f>"Com Direito"</xm:f>
             <x14:dxf>
               <font>
                 <b/>
@@ -3019,9 +3354,9 @@
               </font>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="1" operator="containsText" id="{D1788155-BA8F-42EC-81DF-1B41BB3108EC}">
-            <xm:f>NOT(ISERROR(SEARCH("NÃO",C9)))</xm:f>
-            <xm:f>"NÃO"</xm:f>
+          <x14:cfRule type="containsText" priority="4" operator="containsText" id="{117C5BB4-3198-4851-8D8D-2933B8B56797}">
+            <xm:f>NOT(ISERROR(SEARCH("Sem Direito",C10)))</xm:f>
+            <xm:f>"Sem Direito"</xm:f>
             <x14:dxf>
               <font>
                 <b/>
@@ -3030,7 +3365,7 @@
               </font>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>C9:C48</xm:sqref>
+          <xm:sqref>C10:C49</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>

--- a/templates/salary_map_template.xlsx
+++ b/templates/salary_map_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\F. Martins\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D88600A-CA34-421E-82A0-D5D251FEB78A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7774A0DF-782D-4504-85EB-C12560E2DDC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -377,15 +377,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -416,32 +407,20 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="11">
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF00B050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color theme="5"/>
-      </font>
-    </dxf>
+  <dxfs count="5">
     <dxf>
       <font>
         <b/>
@@ -460,28 +439,7 @@
       <font>
         <b/>
         <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF00B050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF00B050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
+        <color theme="5"/>
       </font>
     </dxf>
     <dxf>
@@ -566,15 +524,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>419100</xdr:colOff>
+      <xdr:colOff>76200</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
+      <xdr:rowOff>25400</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>18419</xdr:colOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>1269369</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>25400</xdr:rowOff>
+      <xdr:rowOff>31750</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -597,8 +555,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10795000" y="241300"/>
-          <a:ext cx="1028069" cy="1295400"/>
+          <a:off x="10452100" y="247650"/>
+          <a:ext cx="1193169" cy="1295400"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -882,8 +840,8 @@
     <col min="1" max="1" width="2.85546875" customWidth="1"/>
     <col min="2" max="2" width="24.140625" customWidth="1"/>
     <col min="3" max="4" width="14.28515625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="21.42578125" style="1" customWidth="1"/>
-    <col min="6" max="10" width="21.42578125" customWidth="1"/>
+    <col min="5" max="5" width="20" style="1" customWidth="1"/>
+    <col min="6" max="10" width="20" customWidth="1"/>
     <col min="11" max="11" width="2.85546875" customWidth="1"/>
     <col min="12" max="16384" width="9.140625" hidden="1"/>
   </cols>
@@ -907,508 +865,508 @@
       <c r="D4" s="6"/>
     </row>
     <row r="6" spans="2:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7"/>
-      <c r="I6" s="7"/>
-      <c r="J6" s="7"/>
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="17"/>
+      <c r="H6" s="17"/>
+      <c r="I6" s="17"/>
+      <c r="J6" s="17"/>
     </row>
     <row r="7" spans="2:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="8"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="8"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
+      <c r="B7" s="18"/>
+      <c r="C7" s="18"/>
+      <c r="D7" s="18"/>
+      <c r="E7" s="18"/>
+      <c r="F7" s="18"/>
+      <c r="G7" s="18"/>
+      <c r="H7" s="18"/>
+      <c r="I7" s="18"/>
+      <c r="J7" s="18"/>
     </row>
     <row r="8" spans="2:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="C8" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9" t="s">
+      <c r="D8" s="19"/>
+      <c r="E8" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="F8" s="9" t="s">
+      <c r="F8" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="G8" s="9" t="s">
+      <c r="G8" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="H8" s="9" t="s">
+      <c r="H8" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="I8" s="9" t="s">
+      <c r="I8" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="J8" s="9" t="s">
+      <c r="J8" s="19" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="9" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="9"/>
+      <c r="B9" s="19"/>
       <c r="C9" s="3" t="s">
         <v>11</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="9"/>
-      <c r="J9" s="9"/>
+      <c r="E9" s="19"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="19"/>
+      <c r="H9" s="19"/>
+      <c r="I9" s="19"/>
+      <c r="J9" s="19"/>
     </row>
     <row r="10" spans="2:10" ht="15" x14ac:dyDescent="0.25">
-      <c r="B10" s="13"/>
-      <c r="C10" s="19"/>
-      <c r="D10" s="10"/>
-      <c r="E10" s="10"/>
-      <c r="F10" s="10"/>
-      <c r="G10" s="10"/>
-      <c r="H10" s="10"/>
-      <c r="I10" s="10"/>
-      <c r="J10" s="14"/>
+      <c r="B10" s="10"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="7"/>
+      <c r="H10" s="7"/>
+      <c r="I10" s="7"/>
+      <c r="J10" s="11"/>
     </row>
     <row r="11" spans="2:10" ht="15" x14ac:dyDescent="0.25">
-      <c r="B11" s="15"/>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="11"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="11"/>
-      <c r="J11" s="16"/>
+      <c r="B11" s="12"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="8"/>
+      <c r="J11" s="13"/>
     </row>
     <row r="12" spans="2:10" ht="15" x14ac:dyDescent="0.25">
-      <c r="B12" s="15"/>
-      <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="11"/>
-      <c r="J12" s="16"/>
+      <c r="B12" s="12"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="13"/>
     </row>
     <row r="13" spans="2:10" ht="15" x14ac:dyDescent="0.25">
-      <c r="B13" s="15"/>
-      <c r="C13" s="11"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="11"/>
-      <c r="H13" s="11"/>
-      <c r="I13" s="11"/>
-      <c r="J13" s="16"/>
+      <c r="B13" s="12"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="8"/>
+      <c r="I13" s="8"/>
+      <c r="J13" s="13"/>
     </row>
     <row r="14" spans="2:10" ht="15" x14ac:dyDescent="0.25">
-      <c r="B14" s="15"/>
-      <c r="C14" s="11"/>
-      <c r="D14" s="11"/>
-      <c r="E14" s="11"/>
-      <c r="F14" s="11"/>
-      <c r="G14" s="11"/>
-      <c r="H14" s="11"/>
-      <c r="I14" s="11"/>
-      <c r="J14" s="16"/>
+      <c r="B14" s="12"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
+      <c r="I14" s="8"/>
+      <c r="J14" s="13"/>
     </row>
     <row r="15" spans="2:10" ht="15" x14ac:dyDescent="0.25">
-      <c r="B15" s="15"/>
-      <c r="C15" s="11"/>
-      <c r="D15" s="11"/>
-      <c r="E15" s="11"/>
-      <c r="F15" s="11"/>
-      <c r="G15" s="11"/>
-      <c r="H15" s="11"/>
-      <c r="I15" s="11"/>
-      <c r="J15" s="16"/>
+      <c r="B15" s="12"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="8"/>
+      <c r="G15" s="8"/>
+      <c r="H15" s="8"/>
+      <c r="I15" s="8"/>
+      <c r="J15" s="13"/>
     </row>
     <row r="16" spans="2:10" ht="15" x14ac:dyDescent="0.25">
-      <c r="B16" s="15"/>
-      <c r="C16" s="11"/>
-      <c r="D16" s="11"/>
-      <c r="E16" s="11"/>
-      <c r="F16" s="11"/>
-      <c r="G16" s="11"/>
-      <c r="H16" s="11"/>
-      <c r="I16" s="11"/>
-      <c r="J16" s="16"/>
+      <c r="B16" s="12"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="8"/>
+      <c r="H16" s="8"/>
+      <c r="I16" s="8"/>
+      <c r="J16" s="13"/>
     </row>
     <row r="17" spans="2:10" ht="15" x14ac:dyDescent="0.25">
-      <c r="B17" s="15"/>
-      <c r="C17" s="11"/>
-      <c r="D17" s="11"/>
-      <c r="E17" s="11"/>
-      <c r="F17" s="11"/>
-      <c r="G17" s="11"/>
-      <c r="H17" s="11"/>
-      <c r="I17" s="11"/>
-      <c r="J17" s="16"/>
+      <c r="B17" s="12"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="8"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="8"/>
+      <c r="I17" s="8"/>
+      <c r="J17" s="13"/>
     </row>
     <row r="18" spans="2:10" ht="15" x14ac:dyDescent="0.25">
-      <c r="B18" s="15"/>
-      <c r="C18" s="11"/>
-      <c r="D18" s="11"/>
-      <c r="E18" s="11"/>
-      <c r="F18" s="11"/>
-      <c r="G18" s="11"/>
-      <c r="H18" s="11"/>
-      <c r="I18" s="11"/>
-      <c r="J18" s="16"/>
+      <c r="B18" s="12"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="8"/>
+      <c r="H18" s="8"/>
+      <c r="I18" s="8"/>
+      <c r="J18" s="13"/>
     </row>
     <row r="19" spans="2:10" ht="15" x14ac:dyDescent="0.25">
-      <c r="B19" s="15"/>
-      <c r="C19" s="11"/>
-      <c r="D19" s="11"/>
-      <c r="E19" s="11"/>
-      <c r="F19" s="11"/>
-      <c r="G19" s="11"/>
-      <c r="H19" s="11"/>
-      <c r="I19" s="11"/>
-      <c r="J19" s="16"/>
+      <c r="B19" s="12"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="8"/>
+      <c r="H19" s="8"/>
+      <c r="I19" s="8"/>
+      <c r="J19" s="13"/>
     </row>
     <row r="20" spans="2:10" ht="15" x14ac:dyDescent="0.25">
-      <c r="B20" s="15"/>
-      <c r="C20" s="11"/>
-      <c r="D20" s="11"/>
-      <c r="E20" s="11"/>
-      <c r="F20" s="11"/>
-      <c r="G20" s="11"/>
-      <c r="H20" s="11"/>
-      <c r="I20" s="11"/>
-      <c r="J20" s="16"/>
+      <c r="B20" s="12"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="8"/>
+      <c r="G20" s="8"/>
+      <c r="H20" s="8"/>
+      <c r="I20" s="8"/>
+      <c r="J20" s="13"/>
     </row>
     <row r="21" spans="2:10" ht="15" x14ac:dyDescent="0.25">
-      <c r="B21" s="15"/>
-      <c r="C21" s="11"/>
-      <c r="D21" s="11"/>
-      <c r="E21" s="11"/>
-      <c r="F21" s="11"/>
-      <c r="G21" s="11"/>
-      <c r="H21" s="11"/>
-      <c r="I21" s="11"/>
-      <c r="J21" s="16"/>
+      <c r="B21" s="12"/>
+      <c r="C21" s="8"/>
+      <c r="D21" s="8"/>
+      <c r="E21" s="8"/>
+      <c r="F21" s="8"/>
+      <c r="G21" s="8"/>
+      <c r="H21" s="8"/>
+      <c r="I21" s="8"/>
+      <c r="J21" s="13"/>
     </row>
     <row r="22" spans="2:10" ht="15" x14ac:dyDescent="0.25">
-      <c r="B22" s="15"/>
-      <c r="C22" s="11"/>
-      <c r="D22" s="11"/>
-      <c r="E22" s="11"/>
-      <c r="F22" s="11"/>
-      <c r="G22" s="11"/>
-      <c r="H22" s="11"/>
-      <c r="I22" s="11"/>
-      <c r="J22" s="16"/>
+      <c r="B22" s="12"/>
+      <c r="C22" s="8"/>
+      <c r="D22" s="8"/>
+      <c r="E22" s="8"/>
+      <c r="F22" s="8"/>
+      <c r="G22" s="8"/>
+      <c r="H22" s="8"/>
+      <c r="I22" s="8"/>
+      <c r="J22" s="13"/>
     </row>
     <row r="23" spans="2:10" ht="15" x14ac:dyDescent="0.25">
-      <c r="B23" s="15"/>
-      <c r="C23" s="11"/>
-      <c r="D23" s="11"/>
-      <c r="E23" s="11"/>
-      <c r="F23" s="11"/>
-      <c r="G23" s="11"/>
-      <c r="H23" s="11"/>
-      <c r="I23" s="11"/>
-      <c r="J23" s="16"/>
+      <c r="B23" s="12"/>
+      <c r="C23" s="8"/>
+      <c r="D23" s="8"/>
+      <c r="E23" s="8"/>
+      <c r="F23" s="8"/>
+      <c r="G23" s="8"/>
+      <c r="H23" s="8"/>
+      <c r="I23" s="8"/>
+      <c r="J23" s="13"/>
     </row>
     <row r="24" spans="2:10" ht="15" x14ac:dyDescent="0.25">
-      <c r="B24" s="15"/>
-      <c r="C24" s="11"/>
-      <c r="D24" s="11"/>
-      <c r="E24" s="11"/>
-      <c r="F24" s="11"/>
-      <c r="G24" s="11"/>
-      <c r="H24" s="11"/>
-      <c r="I24" s="11"/>
-      <c r="J24" s="16"/>
+      <c r="B24" s="12"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="8"/>
+      <c r="H24" s="8"/>
+      <c r="I24" s="8"/>
+      <c r="J24" s="13"/>
     </row>
     <row r="25" spans="2:10" ht="15" x14ac:dyDescent="0.25">
-      <c r="B25" s="15"/>
-      <c r="C25" s="11"/>
-      <c r="D25" s="11"/>
-      <c r="E25" s="11"/>
-      <c r="F25" s="11"/>
-      <c r="G25" s="11"/>
-      <c r="H25" s="11"/>
-      <c r="I25" s="11"/>
-      <c r="J25" s="16"/>
+      <c r="B25" s="12"/>
+      <c r="C25" s="8"/>
+      <c r="D25" s="8"/>
+      <c r="E25" s="8"/>
+      <c r="F25" s="8"/>
+      <c r="G25" s="8"/>
+      <c r="H25" s="8"/>
+      <c r="I25" s="8"/>
+      <c r="J25" s="13"/>
     </row>
     <row r="26" spans="2:10" ht="15" x14ac:dyDescent="0.25">
-      <c r="B26" s="15"/>
-      <c r="C26" s="11"/>
-      <c r="D26" s="11"/>
-      <c r="E26" s="11"/>
-      <c r="F26" s="11"/>
-      <c r="G26" s="11"/>
-      <c r="H26" s="11"/>
-      <c r="I26" s="11"/>
-      <c r="J26" s="16"/>
+      <c r="B26" s="12"/>
+      <c r="C26" s="8"/>
+      <c r="D26" s="8"/>
+      <c r="E26" s="8"/>
+      <c r="F26" s="8"/>
+      <c r="G26" s="8"/>
+      <c r="H26" s="8"/>
+      <c r="I26" s="8"/>
+      <c r="J26" s="13"/>
     </row>
     <row r="27" spans="2:10" ht="15" x14ac:dyDescent="0.25">
-      <c r="B27" s="15"/>
-      <c r="C27" s="11"/>
-      <c r="D27" s="11"/>
-      <c r="E27" s="11"/>
-      <c r="F27" s="11"/>
-      <c r="G27" s="11"/>
-      <c r="H27" s="11"/>
-      <c r="I27" s="11"/>
-      <c r="J27" s="16"/>
+      <c r="B27" s="12"/>
+      <c r="C27" s="8"/>
+      <c r="D27" s="8"/>
+      <c r="E27" s="8"/>
+      <c r="F27" s="8"/>
+      <c r="G27" s="8"/>
+      <c r="H27" s="8"/>
+      <c r="I27" s="8"/>
+      <c r="J27" s="13"/>
     </row>
     <row r="28" spans="2:10" ht="15" x14ac:dyDescent="0.25">
-      <c r="B28" s="15"/>
-      <c r="C28" s="11"/>
-      <c r="D28" s="11"/>
-      <c r="E28" s="11"/>
-      <c r="F28" s="11"/>
-      <c r="G28" s="11"/>
-      <c r="H28" s="11"/>
-      <c r="I28" s="11"/>
-      <c r="J28" s="16"/>
+      <c r="B28" s="12"/>
+      <c r="C28" s="8"/>
+      <c r="D28" s="8"/>
+      <c r="E28" s="8"/>
+      <c r="F28" s="8"/>
+      <c r="G28" s="8"/>
+      <c r="H28" s="8"/>
+      <c r="I28" s="8"/>
+      <c r="J28" s="13"/>
     </row>
     <row r="29" spans="2:10" ht="15" x14ac:dyDescent="0.25">
-      <c r="B29" s="15"/>
-      <c r="C29" s="11"/>
-      <c r="D29" s="11"/>
-      <c r="E29" s="11"/>
-      <c r="F29" s="11"/>
-      <c r="G29" s="11"/>
-      <c r="H29" s="11"/>
-      <c r="I29" s="11"/>
-      <c r="J29" s="16"/>
+      <c r="B29" s="12"/>
+      <c r="C29" s="8"/>
+      <c r="D29" s="8"/>
+      <c r="E29" s="8"/>
+      <c r="F29" s="8"/>
+      <c r="G29" s="8"/>
+      <c r="H29" s="8"/>
+      <c r="I29" s="8"/>
+      <c r="J29" s="13"/>
     </row>
     <row r="30" spans="2:10" ht="15" x14ac:dyDescent="0.25">
-      <c r="B30" s="15"/>
-      <c r="C30" s="11"/>
-      <c r="D30" s="11"/>
-      <c r="E30" s="11"/>
-      <c r="F30" s="11"/>
-      <c r="G30" s="11"/>
-      <c r="H30" s="11"/>
-      <c r="I30" s="11"/>
-      <c r="J30" s="16"/>
+      <c r="B30" s="12"/>
+      <c r="C30" s="8"/>
+      <c r="D30" s="8"/>
+      <c r="E30" s="8"/>
+      <c r="F30" s="8"/>
+      <c r="G30" s="8"/>
+      <c r="H30" s="8"/>
+      <c r="I30" s="8"/>
+      <c r="J30" s="13"/>
     </row>
     <row r="31" spans="2:10" ht="15" x14ac:dyDescent="0.25">
-      <c r="B31" s="15"/>
-      <c r="C31" s="11"/>
-      <c r="D31" s="11"/>
-      <c r="E31" s="11"/>
-      <c r="F31" s="11"/>
-      <c r="G31" s="11"/>
-      <c r="H31" s="11"/>
-      <c r="I31" s="11"/>
-      <c r="J31" s="16"/>
+      <c r="B31" s="12"/>
+      <c r="C31" s="8"/>
+      <c r="D31" s="8"/>
+      <c r="E31" s="8"/>
+      <c r="F31" s="8"/>
+      <c r="G31" s="8"/>
+      <c r="H31" s="8"/>
+      <c r="I31" s="8"/>
+      <c r="J31" s="13"/>
     </row>
     <row r="32" spans="2:10" ht="15" x14ac:dyDescent="0.25">
-      <c r="B32" s="15"/>
-      <c r="C32" s="11"/>
-      <c r="D32" s="11"/>
-      <c r="E32" s="11"/>
-      <c r="F32" s="11"/>
-      <c r="G32" s="11"/>
-      <c r="H32" s="11"/>
-      <c r="I32" s="11"/>
-      <c r="J32" s="16"/>
+      <c r="B32" s="12"/>
+      <c r="C32" s="8"/>
+      <c r="D32" s="8"/>
+      <c r="E32" s="8"/>
+      <c r="F32" s="8"/>
+      <c r="G32" s="8"/>
+      <c r="H32" s="8"/>
+      <c r="I32" s="8"/>
+      <c r="J32" s="13"/>
     </row>
     <row r="33" spans="2:10" ht="15" x14ac:dyDescent="0.25">
-      <c r="B33" s="15"/>
-      <c r="C33" s="11"/>
-      <c r="D33" s="11"/>
-      <c r="E33" s="11"/>
-      <c r="F33" s="11"/>
-      <c r="G33" s="11"/>
-      <c r="H33" s="11"/>
-      <c r="I33" s="11"/>
-      <c r="J33" s="16"/>
+      <c r="B33" s="12"/>
+      <c r="C33" s="8"/>
+      <c r="D33" s="8"/>
+      <c r="E33" s="8"/>
+      <c r="F33" s="8"/>
+      <c r="G33" s="8"/>
+      <c r="H33" s="8"/>
+      <c r="I33" s="8"/>
+      <c r="J33" s="13"/>
     </row>
     <row r="34" spans="2:10" ht="15" x14ac:dyDescent="0.25">
-      <c r="B34" s="15"/>
-      <c r="C34" s="11"/>
-      <c r="D34" s="11"/>
-      <c r="E34" s="11"/>
-      <c r="F34" s="11"/>
-      <c r="G34" s="11"/>
-      <c r="H34" s="11"/>
-      <c r="I34" s="11"/>
-      <c r="J34" s="16"/>
+      <c r="B34" s="12"/>
+      <c r="C34" s="8"/>
+      <c r="D34" s="8"/>
+      <c r="E34" s="8"/>
+      <c r="F34" s="8"/>
+      <c r="G34" s="8"/>
+      <c r="H34" s="8"/>
+      <c r="I34" s="8"/>
+      <c r="J34" s="13"/>
     </row>
     <row r="35" spans="2:10" ht="15" x14ac:dyDescent="0.25">
-      <c r="B35" s="15"/>
-      <c r="C35" s="11"/>
-      <c r="D35" s="11"/>
-      <c r="E35" s="11"/>
-      <c r="F35" s="11"/>
-      <c r="G35" s="11"/>
-      <c r="H35" s="11"/>
-      <c r="I35" s="11"/>
-      <c r="J35" s="16"/>
+      <c r="B35" s="12"/>
+      <c r="C35" s="8"/>
+      <c r="D35" s="8"/>
+      <c r="E35" s="8"/>
+      <c r="F35" s="8"/>
+      <c r="G35" s="8"/>
+      <c r="H35" s="8"/>
+      <c r="I35" s="8"/>
+      <c r="J35" s="13"/>
     </row>
     <row r="36" spans="2:10" ht="15" x14ac:dyDescent="0.25">
-      <c r="B36" s="15"/>
-      <c r="C36" s="11"/>
-      <c r="D36" s="11"/>
-      <c r="E36" s="11"/>
-      <c r="F36" s="11"/>
-      <c r="G36" s="11"/>
-      <c r="H36" s="11"/>
-      <c r="I36" s="11"/>
-      <c r="J36" s="16"/>
+      <c r="B36" s="12"/>
+      <c r="C36" s="8"/>
+      <c r="D36" s="8"/>
+      <c r="E36" s="8"/>
+      <c r="F36" s="8"/>
+      <c r="G36" s="8"/>
+      <c r="H36" s="8"/>
+      <c r="I36" s="8"/>
+      <c r="J36" s="13"/>
     </row>
     <row r="37" spans="2:10" ht="15" x14ac:dyDescent="0.25">
-      <c r="B37" s="15"/>
-      <c r="C37" s="11"/>
-      <c r="D37" s="11"/>
-      <c r="E37" s="11"/>
-      <c r="F37" s="11"/>
-      <c r="G37" s="11"/>
-      <c r="H37" s="11"/>
-      <c r="I37" s="11"/>
-      <c r="J37" s="16"/>
+      <c r="B37" s="12"/>
+      <c r="C37" s="8"/>
+      <c r="D37" s="8"/>
+      <c r="E37" s="8"/>
+      <c r="F37" s="8"/>
+      <c r="G37" s="8"/>
+      <c r="H37" s="8"/>
+      <c r="I37" s="8"/>
+      <c r="J37" s="13"/>
     </row>
     <row r="38" spans="2:10" ht="15" x14ac:dyDescent="0.25">
-      <c r="B38" s="15"/>
-      <c r="C38" s="11"/>
-      <c r="D38" s="11"/>
-      <c r="E38" s="11"/>
-      <c r="F38" s="11"/>
-      <c r="G38" s="11"/>
-      <c r="H38" s="11"/>
-      <c r="I38" s="11"/>
-      <c r="J38" s="16"/>
+      <c r="B38" s="12"/>
+      <c r="C38" s="8"/>
+      <c r="D38" s="8"/>
+      <c r="E38" s="8"/>
+      <c r="F38" s="8"/>
+      <c r="G38" s="8"/>
+      <c r="H38" s="8"/>
+      <c r="I38" s="8"/>
+      <c r="J38" s="13"/>
     </row>
     <row r="39" spans="2:10" ht="15" x14ac:dyDescent="0.25">
-      <c r="B39" s="15"/>
-      <c r="C39" s="11"/>
-      <c r="D39" s="11"/>
-      <c r="E39" s="11"/>
-      <c r="F39" s="11"/>
-      <c r="G39" s="11"/>
-      <c r="H39" s="11"/>
-      <c r="I39" s="11"/>
-      <c r="J39" s="16"/>
+      <c r="B39" s="12"/>
+      <c r="C39" s="8"/>
+      <c r="D39" s="8"/>
+      <c r="E39" s="8"/>
+      <c r="F39" s="8"/>
+      <c r="G39" s="8"/>
+      <c r="H39" s="8"/>
+      <c r="I39" s="8"/>
+      <c r="J39" s="13"/>
     </row>
     <row r="40" spans="2:10" ht="15" x14ac:dyDescent="0.25">
-      <c r="B40" s="15"/>
-      <c r="C40" s="11"/>
-      <c r="D40" s="11"/>
-      <c r="E40" s="11"/>
-      <c r="F40" s="11"/>
-      <c r="G40" s="11"/>
-      <c r="H40" s="11"/>
-      <c r="I40" s="11"/>
-      <c r="J40" s="16"/>
+      <c r="B40" s="12"/>
+      <c r="C40" s="8"/>
+      <c r="D40" s="8"/>
+      <c r="E40" s="8"/>
+      <c r="F40" s="8"/>
+      <c r="G40" s="8"/>
+      <c r="H40" s="8"/>
+      <c r="I40" s="8"/>
+      <c r="J40" s="13"/>
     </row>
     <row r="41" spans="2:10" ht="15" x14ac:dyDescent="0.25">
-      <c r="B41" s="15"/>
-      <c r="C41" s="11"/>
-      <c r="D41" s="11"/>
-      <c r="E41" s="11"/>
-      <c r="F41" s="11"/>
-      <c r="G41" s="11"/>
-      <c r="H41" s="11"/>
-      <c r="I41" s="11"/>
-      <c r="J41" s="16"/>
+      <c r="B41" s="12"/>
+      <c r="C41" s="8"/>
+      <c r="D41" s="8"/>
+      <c r="E41" s="8"/>
+      <c r="F41" s="8"/>
+      <c r="G41" s="8"/>
+      <c r="H41" s="8"/>
+      <c r="I41" s="8"/>
+      <c r="J41" s="13"/>
     </row>
     <row r="42" spans="2:10" ht="15" x14ac:dyDescent="0.25">
-      <c r="B42" s="15"/>
-      <c r="C42" s="11"/>
-      <c r="D42" s="11"/>
-      <c r="E42" s="11"/>
-      <c r="F42" s="11"/>
-      <c r="G42" s="11"/>
-      <c r="H42" s="11"/>
-      <c r="I42" s="11"/>
-      <c r="J42" s="16"/>
+      <c r="B42" s="12"/>
+      <c r="C42" s="8"/>
+      <c r="D42" s="8"/>
+      <c r="E42" s="8"/>
+      <c r="F42" s="8"/>
+      <c r="G42" s="8"/>
+      <c r="H42" s="8"/>
+      <c r="I42" s="8"/>
+      <c r="J42" s="13"/>
     </row>
     <row r="43" spans="2:10" ht="15" x14ac:dyDescent="0.25">
-      <c r="B43" s="15"/>
-      <c r="C43" s="11"/>
-      <c r="D43" s="11"/>
-      <c r="E43" s="11"/>
-      <c r="F43" s="11"/>
-      <c r="G43" s="11"/>
-      <c r="H43" s="11"/>
-      <c r="I43" s="11"/>
-      <c r="J43" s="16"/>
+      <c r="B43" s="12"/>
+      <c r="C43" s="8"/>
+      <c r="D43" s="8"/>
+      <c r="E43" s="8"/>
+      <c r="F43" s="8"/>
+      <c r="G43" s="8"/>
+      <c r="H43" s="8"/>
+      <c r="I43" s="8"/>
+      <c r="J43" s="13"/>
     </row>
     <row r="44" spans="2:10" ht="15" x14ac:dyDescent="0.25">
-      <c r="B44" s="15"/>
-      <c r="C44" s="11"/>
-      <c r="D44" s="11"/>
-      <c r="E44" s="11"/>
-      <c r="F44" s="11"/>
-      <c r="G44" s="11"/>
-      <c r="H44" s="11"/>
-      <c r="I44" s="11"/>
-      <c r="J44" s="16"/>
+      <c r="B44" s="12"/>
+      <c r="C44" s="8"/>
+      <c r="D44" s="8"/>
+      <c r="E44" s="8"/>
+      <c r="F44" s="8"/>
+      <c r="G44" s="8"/>
+      <c r="H44" s="8"/>
+      <c r="I44" s="8"/>
+      <c r="J44" s="13"/>
     </row>
     <row r="45" spans="2:10" ht="15" x14ac:dyDescent="0.25">
-      <c r="B45" s="15"/>
-      <c r="C45" s="11"/>
-      <c r="D45" s="11"/>
-      <c r="E45" s="11"/>
-      <c r="F45" s="11"/>
-      <c r="G45" s="11"/>
-      <c r="H45" s="11"/>
-      <c r="I45" s="11"/>
-      <c r="J45" s="16"/>
+      <c r="B45" s="12"/>
+      <c r="C45" s="8"/>
+      <c r="D45" s="8"/>
+      <c r="E45" s="8"/>
+      <c r="F45" s="8"/>
+      <c r="G45" s="8"/>
+      <c r="H45" s="8"/>
+      <c r="I45" s="8"/>
+      <c r="J45" s="13"/>
     </row>
     <row r="46" spans="2:10" ht="15" x14ac:dyDescent="0.25">
-      <c r="B46" s="15"/>
-      <c r="C46" s="11"/>
-      <c r="D46" s="11"/>
-      <c r="E46" s="11"/>
-      <c r="F46" s="11"/>
-      <c r="G46" s="11"/>
-      <c r="H46" s="11"/>
-      <c r="I46" s="11"/>
-      <c r="J46" s="16"/>
+      <c r="B46" s="12"/>
+      <c r="C46" s="8"/>
+      <c r="D46" s="8"/>
+      <c r="E46" s="8"/>
+      <c r="F46" s="8"/>
+      <c r="G46" s="8"/>
+      <c r="H46" s="8"/>
+      <c r="I46" s="8"/>
+      <c r="J46" s="13"/>
     </row>
     <row r="47" spans="2:10" ht="15" x14ac:dyDescent="0.25">
-      <c r="B47" s="15"/>
-      <c r="C47" s="11"/>
-      <c r="D47" s="11"/>
-      <c r="E47" s="11"/>
-      <c r="F47" s="11"/>
-      <c r="G47" s="11"/>
-      <c r="H47" s="11"/>
-      <c r="I47" s="11"/>
-      <c r="J47" s="16"/>
+      <c r="B47" s="12"/>
+      <c r="C47" s="8"/>
+      <c r="D47" s="8"/>
+      <c r="E47" s="8"/>
+      <c r="F47" s="8"/>
+      <c r="G47" s="8"/>
+      <c r="H47" s="8"/>
+      <c r="I47" s="8"/>
+      <c r="J47" s="13"/>
     </row>
     <row r="48" spans="2:10" ht="15" x14ac:dyDescent="0.25">
-      <c r="B48" s="15"/>
-      <c r="C48" s="11"/>
-      <c r="D48" s="11"/>
-      <c r="E48" s="11"/>
-      <c r="F48" s="11"/>
-      <c r="G48" s="11"/>
-      <c r="H48" s="11"/>
-      <c r="I48" s="11"/>
-      <c r="J48" s="16"/>
+      <c r="B48" s="12"/>
+      <c r="C48" s="8"/>
+      <c r="D48" s="8"/>
+      <c r="E48" s="8"/>
+      <c r="F48" s="8"/>
+      <c r="G48" s="8"/>
+      <c r="H48" s="8"/>
+      <c r="I48" s="8"/>
+      <c r="J48" s="13"/>
     </row>
     <row r="49" spans="2:10" ht="15" x14ac:dyDescent="0.25">
-      <c r="B49" s="17"/>
-      <c r="C49" s="12"/>
-      <c r="D49" s="12"/>
-      <c r="E49" s="12"/>
-      <c r="F49" s="12"/>
-      <c r="G49" s="12"/>
-      <c r="H49" s="12"/>
-      <c r="I49" s="12"/>
-      <c r="J49" s="18"/>
+      <c r="B49" s="14"/>
+      <c r="C49" s="9"/>
+      <c r="D49" s="9"/>
+      <c r="E49" s="9"/>
+      <c r="F49" s="9"/>
+      <c r="G49" s="9"/>
+      <c r="H49" s="9"/>
+      <c r="I49" s="9"/>
+      <c r="J49" s="15"/>
     </row>
     <row r="50" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B50" s="2"/>
@@ -3326,14 +3284,14 @@
     <mergeCell ref="C8:D8"/>
   </mergeCells>
   <conditionalFormatting sqref="D10:D49">
-    <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
-      <formula>"Pago"</formula>
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
+      <formula>"Pendente"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
       <formula>"Sem Direito"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
-      <formula>"Pendente"</formula>
+    <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
+      <formula>"Pago"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3343,6 +3301,17 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="4" operator="containsText" id="{117C5BB4-3198-4851-8D8D-2933B8B56797}">
+            <xm:f>NOT(ISERROR(SEARCH("Sem Direito",C10)))</xm:f>
+            <xm:f>"Sem Direito"</xm:f>
+            <x14:dxf>
+              <font>
+                <b/>
+                <i val="0"/>
+                <color rgb="FFFF0000"/>
+              </font>
+            </x14:dxf>
+          </x14:cfRule>
           <x14:cfRule type="containsText" priority="5" operator="containsText" id="{761CD187-0092-47F8-B02D-8C36014B61AA}">
             <xm:f>NOT(ISERROR(SEARCH("Com Direito",C10)))</xm:f>
             <xm:f>"Com Direito"</xm:f>
@@ -3354,17 +3323,6 @@
               </font>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="4" operator="containsText" id="{117C5BB4-3198-4851-8D8D-2933B8B56797}">
-            <xm:f>NOT(ISERROR(SEARCH("Sem Direito",C10)))</xm:f>
-            <xm:f>"Sem Direito"</xm:f>
-            <x14:dxf>
-              <font>
-                <b/>
-                <i val="0"/>
-                <color rgb="FFFF0000"/>
-              </font>
-            </x14:dxf>
-          </x14:cfRule>
           <xm:sqref>C10:C49</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
